--- a/Data/Raw_burials/c14_raw_burials.xlsx
+++ b/Data/Raw_burials/c14_raw_burials.xlsx
@@ -158,7 +158,7 @@
     <t>BETA210652</t>
   </si>
   <si>
-    <t>Antolín et al., 2011</t>
+    <t>Antolín et al., 2016</t>
   </si>
   <si>
     <t>Cova dels Lladres</t>
@@ -224,7 +224,7 @@
     <t>CNA2319 </t>
   </si>
   <si>
-    <t>Gibaja et al., 2017</t>
+    <t>Gibaja et al., 2017a</t>
   </si>
   <si>
     <t>G-10</t>
@@ -242,7 +242,7 @@
     <t>UBAR101</t>
   </si>
   <si>
-    <t>Rosillo et al., 2022</t>
+    <t>Rosillo et al., 2025</t>
   </si>
   <si>
     <t>Bòbila Madurell-Madurell Sud</t>
@@ -260,6 +260,9 @@
     <t>UBAR1282</t>
   </si>
   <si>
+    <t>Gibaja et al., 2017b</t>
+  </si>
+  <si>
     <t>E27</t>
   </si>
   <si>
@@ -302,7 +305,7 @@
     <t>MC2139</t>
   </si>
   <si>
-    <t>Guilaine et al., 1982</t>
+    <t>Cebrià et al., 2014</t>
   </si>
   <si>
     <t>Els Cirerers</t>
@@ -311,7 +314,7 @@
     <t>No reference-1</t>
   </si>
   <si>
-    <t>Mestres and Martín, 1996</t>
+    <t>Mestres  et al., 1996</t>
   </si>
   <si>
     <t>Bòbila Madurell-Can Gambús 2</t>
@@ -323,9 +326,6 @@
     <t>CNA2301</t>
   </si>
   <si>
-    <t>Bravo et al., 2015</t>
-  </si>
-  <si>
     <t>E60</t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>UBAR583</t>
   </si>
   <si>
-    <t>Mestres, 2007</t>
+    <t>Farré, 2007</t>
   </si>
   <si>
     <t>Hort d'en Grimau</t>
@@ -737,6 +737,9 @@
     <t>LTL5028A</t>
   </si>
   <si>
+    <t>Bravo et al., 2014</t>
+  </si>
+  <si>
     <t>Vilar de Simosa</t>
   </si>
   <si>
@@ -893,7 +896,7 @@
     <t>UBAR1013</t>
   </si>
   <si>
-    <t>Pou and Martí in press</t>
+    <t>Matas and Roig, 2017</t>
   </si>
   <si>
     <t>B16</t>
@@ -1064,15 +1067,15 @@
     <t>BETA252115</t>
   </si>
   <si>
+    <t>Masferrer et al., 2010; Morell et al., 2018</t>
+  </si>
+  <si>
     <t>Mina 28</t>
   </si>
   <si>
     <t>UBAR47</t>
   </si>
   <si>
-    <t>Masferrer et al., 2010</t>
-  </si>
-  <si>
     <t>Bòbila d'en Joca</t>
   </si>
   <si>
@@ -1086,9 +1089,6 @@
   </si>
   <si>
     <t>UBAR903 </t>
-  </si>
-  <si>
-    <t>Martín and Casas in press</t>
   </si>
   <si>
     <t>M-7-Indv. 1</t>
@@ -1131,7 +1131,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1148,12 +1148,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1177,7 +1171,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1219,9 +1213,6 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -2796,7 +2787,7 @@
         <v>0.0</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
@@ -2815,7 +2806,7 @@
         <v>32</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" s="7">
         <v>1.6970351996066801</v>
@@ -2824,7 +2815,7 @@
         <v>41.33613124307957</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G22" s="9">
         <v>5245.0</v>
@@ -2876,10 +2867,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" s="7">
         <v>1.7130154745011708</v>
@@ -2888,7 +2879,7 @@
         <v>41.33236807120096</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G23" s="9">
         <v>5240.0</v>
@@ -2943,7 +2934,7 @@
         <v>65</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" s="7">
         <v>2.090537008463704</v>
@@ -2952,7 +2943,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G24" s="9">
         <v>5225.0</v>
@@ -3007,7 +2998,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D25" s="7">
         <v>2.130499754696959</v>
@@ -3016,7 +3007,7 @@
         <v>41.53961305750816</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" s="9">
         <v>5220.0</v>
@@ -3071,7 +3062,7 @@
         <v>75</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="7">
         <v>2.090537008463704</v>
@@ -3080,7 +3071,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G26" s="9">
         <v>5210.0</v>
@@ -3132,10 +3123,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" s="7">
         <v>2.150195216215055</v>
@@ -3144,7 +3135,7 @@
         <v>41.80701765741211</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G27" s="9">
         <v>5210.0</v>
@@ -3180,7 +3171,7 @@
         <v>0.0</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
@@ -3196,7 +3187,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>52</v>
@@ -3208,7 +3199,7 @@
         <v>41.351443134908</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G28" s="9">
         <v>5205.0</v>
@@ -3244,7 +3235,7 @@
         <v>0.0</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -3260,10 +3251,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" s="7">
         <v>2.090537008463704</v>
@@ -3272,7 +3263,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G29" s="9">
         <v>5200.0</v>
@@ -3308,7 +3299,7 @@
         <v>0.0</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -3324,7 +3315,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>102</v>
@@ -3436,7 +3427,7 @@
         <v>0.0</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
@@ -3500,7 +3491,7 @@
         <v>0.0</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
@@ -3516,7 +3507,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>108</v>
@@ -3564,7 +3555,7 @@
         <v>0.0</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
@@ -3628,7 +3619,7 @@
         <v>0.0</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
@@ -3692,7 +3683,7 @@
         <v>0.0</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
@@ -3756,7 +3747,7 @@
         <v>0.0</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
@@ -3948,7 +3939,7 @@
         <v>0.0</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
@@ -4012,7 +4003,7 @@
         <v>0.0</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
@@ -4076,7 +4067,7 @@
         <v>0.0</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
@@ -4156,7 +4147,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>136</v>
@@ -4332,7 +4323,7 @@
         <v>0.0</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
@@ -4460,7 +4451,7 @@
         <v>0.0</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
@@ -4524,7 +4515,7 @@
         <v>0.0</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -4716,7 +4707,7 @@
         <v>0.0</v>
       </c>
       <c r="R51" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
@@ -4780,7 +4771,7 @@
         <v>0.0</v>
       </c>
       <c r="R52" s="10" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
@@ -4844,7 +4835,7 @@
         <v>0.0</v>
       </c>
       <c r="R53" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
@@ -5228,7 +5219,7 @@
         <v>0.0</v>
       </c>
       <c r="R59" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
@@ -5484,7 +5475,7 @@
         <v>0.0</v>
       </c>
       <c r="R63" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
@@ -5548,7 +5539,7 @@
         <v>0.0</v>
       </c>
       <c r="R64" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
@@ -5612,7 +5603,7 @@
         <v>0.0</v>
       </c>
       <c r="R65" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
@@ -6060,7 +6051,7 @@
         <v>0.0</v>
       </c>
       <c r="R72" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
@@ -6444,7 +6435,7 @@
         <v>0.0</v>
       </c>
       <c r="R78" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
@@ -6508,7 +6499,7 @@
         <v>0.0</v>
       </c>
       <c r="R79" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
@@ -6764,7 +6755,7 @@
         <v>0.0</v>
       </c>
       <c r="R83" s="10" t="s">
-        <v>101</v>
+        <v>239</v>
       </c>
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
@@ -6780,10 +6771,10 @@
         <v>83.0</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D84" s="7">
         <v>1.5883906328061166</v>
@@ -6792,7 +6783,7 @@
         <v>41.99802789146873</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G84" s="9">
         <v>4984.0</v>
@@ -6847,7 +6838,7 @@
         <v>144</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D85" s="7">
         <v>2.090537008463704</v>
@@ -6856,7 +6847,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G85" s="9">
         <v>4982.0</v>
@@ -6911,7 +6902,7 @@
         <v>144</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D86" s="7">
         <v>2.090537008463704</v>
@@ -6920,7 +6911,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G86" s="9">
         <v>4980.0</v>
@@ -6956,7 +6947,7 @@
         <v>0.0</v>
       </c>
       <c r="R86" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
@@ -6975,7 +6966,7 @@
         <v>126</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D87" s="7">
         <v>2.8146485891203645</v>
@@ -6984,7 +6975,7 @@
         <v>41.99798531007377</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G87" s="9">
         <v>4980.0</v>
@@ -7020,7 +7011,7 @@
         <v>0.0</v>
       </c>
       <c r="R87" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
@@ -7036,10 +7027,10 @@
         <v>87.0</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D88" s="7">
         <v>1.537425094293886</v>
@@ -7048,7 +7039,7 @@
         <v>41.92686953937767</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G88" s="9">
         <v>4979.0</v>
@@ -7103,7 +7094,7 @@
         <v>144</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D89" s="7">
         <v>2.090537008463704</v>
@@ -7112,7 +7103,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G89" s="9">
         <v>4978.0</v>
@@ -7167,7 +7158,7 @@
         <v>144</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D90" s="7">
         <v>2.090537008463704</v>
@@ -7176,7 +7167,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G90" s="9">
         <v>4975.0</v>
@@ -7231,7 +7222,7 @@
         <v>144</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D91" s="7">
         <v>2.090537008463704</v>
@@ -7240,7 +7231,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G91" s="9">
         <v>4975.0</v>
@@ -7295,7 +7286,7 @@
         <v>138</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D92" s="7">
         <v>2.2994585584087797</v>
@@ -7304,7 +7295,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G92" s="9">
         <v>4975.0</v>
@@ -7356,10 +7347,10 @@
         <v>92.0</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D93" s="7">
         <v>1.6778823209988234</v>
@@ -7368,7 +7359,7 @@
         <v>41.97356042506945</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G93" s="9">
         <v>4965.0</v>
@@ -7423,7 +7414,7 @@
         <v>126</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D94" s="7">
         <v>2.8146485891203645</v>
@@ -7432,7 +7423,7 @@
         <v>41.99798531007377</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G94" s="9">
         <v>4965.0</v>
@@ -7487,7 +7478,7 @@
         <v>144</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D95" s="7">
         <v>2.090537008463704</v>
@@ -7496,7 +7487,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G95" s="9">
         <v>4955.0</v>
@@ -7548,10 +7539,10 @@
         <v>95.0</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D96" s="7">
         <v>1.384342090972301</v>
@@ -7560,7 +7551,7 @@
         <v>42.01757331140867</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G96" s="9">
         <v>4951.0</v>
@@ -7615,7 +7606,7 @@
         <v>138</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D97" s="7">
         <v>2.2994585584087797</v>
@@ -7624,7 +7615,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G97" s="9">
         <v>4950.0</v>
@@ -7676,10 +7667,10 @@
         <v>97.0</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D98" s="7">
         <v>2.788864521086892</v>
@@ -7688,7 +7679,7 @@
         <v>41.92913386656426</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G98" s="9">
         <v>4950.0</v>
@@ -7724,7 +7715,7 @@
         <v>0.0</v>
       </c>
       <c r="R98" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
@@ -7740,10 +7731,10 @@
         <v>98.0</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D99" s="7">
         <v>1.3403677734879984</v>
@@ -7752,7 +7743,7 @@
         <v>41.98319929654655</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G99" s="9">
         <v>4950.0</v>
@@ -7788,7 +7779,7 @@
         <v>0.0</v>
       </c>
       <c r="R99" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
@@ -7804,10 +7795,10 @@
         <v>99.0</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D100" s="7">
         <v>1.86333327663719</v>
@@ -7816,7 +7807,7 @@
         <v>41.7194444384622</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G100" s="9">
         <v>4947.0</v>
@@ -7852,7 +7843,7 @@
         <v>0.0</v>
       </c>
       <c r="R100" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
@@ -7868,10 +7859,10 @@
         <v>100.0</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D101" s="7">
         <v>2.0886885994891364</v>
@@ -7880,7 +7871,7 @@
         <v>41.617768967991275</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G101" s="9">
         <v>4945.0</v>
@@ -7916,7 +7907,7 @@
         <v>0.0</v>
       </c>
       <c r="R101" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
@@ -7935,7 +7926,7 @@
         <v>144</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D102" s="7">
         <v>2.090537008463704</v>
@@ -7944,7 +7935,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G102" s="9">
         <v>4940.0</v>
@@ -7996,10 +7987,10 @@
         <v>102.0</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D103" s="7">
         <v>2.0823474533204696</v>
@@ -8008,7 +7999,7 @@
         <v>41.49170741204426</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G103" s="9">
         <v>4920.0</v>
@@ -8043,8 +8034,8 @@
       <c r="Q103" s="8">
         <v>0.0</v>
       </c>
-      <c r="R103" s="14" t="s">
-        <v>291</v>
+      <c r="R103" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
@@ -8063,7 +8054,7 @@
         <v>112</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D104" s="7">
         <v>2.090537008463704</v>
@@ -8072,7 +8063,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G104" s="9">
         <v>4895.0</v>
@@ -8108,7 +8099,7 @@
         <v>0.0</v>
       </c>
       <c r="R104" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
@@ -8124,10 +8115,10 @@
         <v>104.0</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D105" s="7">
         <v>1.7130154745011708</v>
@@ -8136,7 +8127,7 @@
         <v>41.33236807120096</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G105" s="9">
         <v>4890.0</v>
@@ -8191,7 +8182,7 @@
         <v>232</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D106" s="7">
         <v>2.0001516349770174</v>
@@ -8200,7 +8191,7 @@
         <v>41.309934468445284</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G106" s="9">
         <v>4880.0</v>
@@ -8255,7 +8246,7 @@
         <v>138</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D107" s="7">
         <v>2.2994585584087797</v>
@@ -8264,7 +8255,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G107" s="9">
         <v>4880.0</v>
@@ -8316,10 +8307,10 @@
         <v>107.0</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D108" s="7">
         <v>1.6615680543409397</v>
@@ -8328,7 +8319,7 @@
         <v>41.35112907639807</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G108" s="9">
         <v>4870.0</v>
@@ -8383,7 +8374,7 @@
         <v>144</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D109" s="7">
         <v>2.090537008463704</v>
@@ -8392,7 +8383,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G109" s="9">
         <v>4865.0</v>
@@ -8444,10 +8435,10 @@
         <v>109.0</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D110" s="7">
         <v>1.341081332086459</v>
@@ -8456,7 +8447,7 @@
         <v>41.98314656870753</v>
       </c>
       <c r="F110" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G110" s="9">
         <v>4860.0</v>
@@ -8508,10 +8499,10 @@
         <v>110.0</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D111" s="7">
         <v>2.090537368049478</v>
@@ -8520,7 +8511,7 @@
         <v>41.534237172160196</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G111" s="9">
         <v>4857.0</v>
@@ -8556,7 +8547,7 @@
         <v>1.0</v>
       </c>
       <c r="R111" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
@@ -8572,10 +8563,10 @@
         <v>111.0</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D112" s="7">
         <v>1.4077285426520507</v>
@@ -8584,7 +8575,7 @@
         <v>41.99658230022616</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G112" s="9">
         <v>4855.0</v>
@@ -8639,7 +8630,7 @@
         <v>144</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D113" s="7">
         <v>2.090537008463704</v>
@@ -8648,7 +8639,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G113" s="9">
         <v>4850.0</v>
@@ -8703,7 +8694,7 @@
         <v>138</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D114" s="7">
         <v>2.2994585584087797</v>
@@ -8712,7 +8703,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G114" s="9">
         <v>4840.0</v>
@@ -8764,10 +8755,10 @@
         <v>114.0</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D115" s="7">
         <v>1.62749417945922</v>
@@ -8776,7 +8767,7 @@
         <v>41.91275167661886</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G115" s="9">
         <v>4800.0</v>
@@ -8831,7 +8822,7 @@
         <v>138</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D116" s="7">
         <v>2.2994585584087797</v>
@@ -8840,7 +8831,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G116" s="9">
         <v>4798.0</v>
@@ -8895,7 +8886,7 @@
         <v>138</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D117" s="7">
         <v>2.2994585584087797</v>
@@ -8904,7 +8895,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G117" s="9">
         <v>4790.0</v>
@@ -8959,7 +8950,7 @@
         <v>144</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D118" s="7">
         <v>2.090537008463704</v>
@@ -8968,7 +8959,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G118" s="9">
         <v>4775.0</v>
@@ -9023,7 +9014,7 @@
         <v>144</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D119" s="7">
         <v>2.090537008463704</v>
@@ -9032,7 +9023,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G119" s="9">
         <v>4770.0</v>
@@ -9087,7 +9078,7 @@
         <v>138</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D120" s="7">
         <v>2.2994585584087797</v>
@@ -9096,7 +9087,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G120" s="9">
         <v>4760.0</v>
@@ -9148,10 +9139,10 @@
         <v>120.0</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D121" s="7">
         <v>1.7741399025973532</v>
@@ -9160,7 +9151,7 @@
         <v>42.07457290664265</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G121" s="9">
         <v>4759.0</v>
@@ -9212,10 +9203,10 @@
         <v>121.0</v>
       </c>
       <c r="B122" s="8" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D122" s="7">
         <v>1.5871856337557653</v>
@@ -9224,7 +9215,7 @@
         <v>41.422283608218606</v>
       </c>
       <c r="F122" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G122" s="9">
         <v>4740.0</v>
@@ -9260,7 +9251,7 @@
         <v>0.0</v>
       </c>
       <c r="R122" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
@@ -9276,10 +9267,10 @@
         <v>122.0</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D123" s="7">
         <v>1.341081332086459</v>
@@ -9288,7 +9279,7 @@
         <v>41.98314656870753</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G123" s="9">
         <v>4723.0</v>
@@ -9343,7 +9334,7 @@
         <v>32</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D124" s="7">
         <v>1.6970351996066801</v>
@@ -9352,7 +9343,7 @@
         <v>41.33613124307957</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G124" s="9">
         <v>4690.0</v>
@@ -9388,7 +9379,7 @@
         <v>0.0</v>
       </c>
       <c r="R124" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
@@ -9407,7 +9398,7 @@
         <v>138</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D125" s="7">
         <v>2.2994585584087797</v>
@@ -9416,7 +9407,7 @@
         <v>41.59697183617283</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G125" s="9">
         <v>4669.0</v>
@@ -9471,7 +9462,7 @@
         <v>232</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D126" s="7">
         <v>2.0001516349770174</v>
@@ -9480,7 +9471,7 @@
         <v>41.309934468445284</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G126" s="9">
         <v>4658.0</v>
@@ -9532,10 +9523,10 @@
         <v>126.0</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D127" s="7">
         <v>3.176274567616859</v>
@@ -9544,7 +9535,7 @@
         <v>42.05711887934744</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G127" s="9">
         <v>4630.0</v>
@@ -9580,7 +9571,7 @@
         <v>0.0</v>
       </c>
       <c r="R127" s="10" t="s">
-        <v>141</v>
+        <v>349</v>
       </c>
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
@@ -9599,7 +9590,7 @@
         <v>232</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D128" s="7">
         <v>2.0001516349770174</v>
@@ -9608,7 +9599,7 @@
         <v>41.309934468445284</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G128" s="9">
         <v>4610.0</v>
@@ -9644,7 +9635,7 @@
         <v>0.0</v>
       </c>
       <c r="R128" s="10" t="s">
-        <v>350</v>
+        <v>135</v>
       </c>
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
@@ -9660,10 +9651,10 @@
         <v>128.0</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D129" s="7">
         <v>2.269316216182102</v>
@@ -9672,7 +9663,7 @@
         <v>41.54378552531113</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G129" s="9">
         <v>4600.0</v>
@@ -9727,7 +9718,7 @@
         <v>144</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D130" s="7">
         <v>2.090537008463704</v>
@@ -9736,7 +9727,7 @@
         <v>41.53423716931625</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G130" s="9">
         <v>4570.0</v>
@@ -9771,8 +9762,8 @@
       <c r="Q130" s="8">
         <v>0.0</v>
       </c>
-      <c r="R130" s="14" t="s">
-        <v>356</v>
+      <c r="R130" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
@@ -9836,7 +9827,7 @@
         <v>0.0</v>
       </c>
       <c r="R131" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
@@ -9852,10 +9843,10 @@
         <v>131.0</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D132" s="7">
         <v>1.341081332086459</v>
@@ -9912,14 +9903,14 @@
       <c r="Z132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="15"/>
+      <c r="A133" s="14"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
       <c r="F133" s="3"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="16"/>
+      <c r="G133" s="15"/>
+      <c r="H133" s="15"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -9940,7 +9931,7 @@
       <c r="Z133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="15"/>
+      <c r="A134" s="14"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="2"/>
@@ -9968,7 +9959,7 @@
       <c r="Z134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="15"/>
+      <c r="A135" s="14"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="2"/>
@@ -9996,7 +9987,7 @@
       <c r="Z135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="15"/>
+      <c r="A136" s="14"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="2"/>
@@ -10024,7 +10015,7 @@
       <c r="Z136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="15"/>
+      <c r="A137" s="14"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="2"/>
@@ -10052,7 +10043,7 @@
       <c r="Z137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="15"/>
+      <c r="A138" s="14"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="2"/>
@@ -10080,7 +10071,7 @@
       <c r="Z138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="15"/>
+      <c r="A139" s="14"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="2"/>
@@ -10108,7 +10099,7 @@
       <c r="Z139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="15"/>
+      <c r="A140" s="14"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="2"/>
@@ -10136,7 +10127,7 @@
       <c r="Z140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="15"/>
+      <c r="A141" s="14"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="2"/>
@@ -10164,7 +10155,7 @@
       <c r="Z141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="15"/>
+      <c r="A142" s="14"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="2"/>
@@ -10192,7 +10183,7 @@
       <c r="Z142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="15"/>
+      <c r="A143" s="14"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="2"/>
@@ -10220,7 +10211,7 @@
       <c r="Z143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="15"/>
+      <c r="A144" s="14"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="2"/>
@@ -10248,7 +10239,7 @@
       <c r="Z144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="15"/>
+      <c r="A145" s="14"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="2"/>
@@ -10276,7 +10267,7 @@
       <c r="Z145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="15"/>
+      <c r="A146" s="14"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="2"/>
@@ -10304,7 +10295,7 @@
       <c r="Z146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="15"/>
+      <c r="A147" s="14"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="2"/>
@@ -10332,7 +10323,7 @@
       <c r="Z147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="15"/>
+      <c r="A148" s="14"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="2"/>
@@ -10360,7 +10351,7 @@
       <c r="Z148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="15"/>
+      <c r="A149" s="14"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="2"/>
@@ -10388,7 +10379,7 @@
       <c r="Z149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="15"/>
+      <c r="A150" s="14"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="2"/>
@@ -10416,7 +10407,7 @@
       <c r="Z150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="15"/>
+      <c r="A151" s="14"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="2"/>
@@ -10444,7 +10435,7 @@
       <c r="Z151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="15"/>
+      <c r="A152" s="14"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="2"/>
@@ -10472,7 +10463,7 @@
       <c r="Z152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="15"/>
+      <c r="A153" s="14"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="2"/>
@@ -10500,7 +10491,7 @@
       <c r="Z153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="15"/>
+      <c r="A154" s="14"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="2"/>
@@ -10528,7 +10519,7 @@
       <c r="Z154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="15"/>
+      <c r="A155" s="14"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="2"/>
@@ -10556,7 +10547,7 @@
       <c r="Z155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="15"/>
+      <c r="A156" s="14"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="2"/>
@@ -10584,7 +10575,7 @@
       <c r="Z156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="15"/>
+      <c r="A157" s="14"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="2"/>
@@ -10612,7 +10603,7 @@
       <c r="Z157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="15"/>
+      <c r="A158" s="14"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="2"/>
@@ -10640,7 +10631,7 @@
       <c r="Z158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="15"/>
+      <c r="A159" s="14"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="2"/>
@@ -10668,7 +10659,7 @@
       <c r="Z159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="15"/>
+      <c r="A160" s="14"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="2"/>
@@ -10696,7 +10687,7 @@
       <c r="Z160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="15"/>
+      <c r="A161" s="14"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="2"/>
@@ -10724,7 +10715,7 @@
       <c r="Z161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="15"/>
+      <c r="A162" s="14"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="2"/>
@@ -10752,7 +10743,7 @@
       <c r="Z162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="15"/>
+      <c r="A163" s="14"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="2"/>
@@ -10780,7 +10771,7 @@
       <c r="Z163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="15"/>
+      <c r="A164" s="14"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="2"/>
@@ -10808,7 +10799,7 @@
       <c r="Z164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="15"/>
+      <c r="A165" s="14"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="2"/>
@@ -10836,7 +10827,7 @@
       <c r="Z165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="15"/>
+      <c r="A166" s="14"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="2"/>
@@ -10864,7 +10855,7 @@
       <c r="Z166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="15"/>
+      <c r="A167" s="14"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="2"/>
@@ -10892,7 +10883,7 @@
       <c r="Z167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="15"/>
+      <c r="A168" s="14"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="2"/>
@@ -10920,7 +10911,7 @@
       <c r="Z168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="15"/>
+      <c r="A169" s="14"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="2"/>
@@ -10948,7 +10939,7 @@
       <c r="Z169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="15"/>
+      <c r="A170" s="14"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="2"/>
@@ -10976,7 +10967,7 @@
       <c r="Z170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="15"/>
+      <c r="A171" s="14"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="2"/>
@@ -11004,7 +10995,7 @@
       <c r="Z171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="15"/>
+      <c r="A172" s="14"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="2"/>
@@ -11032,7 +11023,7 @@
       <c r="Z172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="15"/>
+      <c r="A173" s="14"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="2"/>
@@ -11060,7 +11051,7 @@
       <c r="Z173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="15"/>
+      <c r="A174" s="14"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="2"/>
@@ -11088,7 +11079,7 @@
       <c r="Z174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="15"/>
+      <c r="A175" s="14"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="2"/>
@@ -11116,7 +11107,7 @@
       <c r="Z175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="15"/>
+      <c r="A176" s="14"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="2"/>
@@ -11144,7 +11135,7 @@
       <c r="Z176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="15"/>
+      <c r="A177" s="14"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="2"/>
@@ -11172,7 +11163,7 @@
       <c r="Z177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="15"/>
+      <c r="A178" s="14"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="2"/>
@@ -11200,7 +11191,7 @@
       <c r="Z178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="15"/>
+      <c r="A179" s="14"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="2"/>
@@ -11228,7 +11219,7 @@
       <c r="Z179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="15"/>
+      <c r="A180" s="14"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="2"/>
@@ -11256,7 +11247,7 @@
       <c r="Z180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="15"/>
+      <c r="A181" s="14"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="2"/>
@@ -11284,7 +11275,7 @@
       <c r="Z181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="15"/>
+      <c r="A182" s="14"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="2"/>
@@ -11312,7 +11303,7 @@
       <c r="Z182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="15"/>
+      <c r="A183" s="14"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="2"/>
@@ -11340,7 +11331,7 @@
       <c r="Z183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="15"/>
+      <c r="A184" s="14"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="2"/>
@@ -11368,7 +11359,7 @@
       <c r="Z184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="15"/>
+      <c r="A185" s="14"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="2"/>
@@ -11396,7 +11387,7 @@
       <c r="Z185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="15"/>
+      <c r="A186" s="14"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="2"/>
@@ -11424,7 +11415,7 @@
       <c r="Z186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="15"/>
+      <c r="A187" s="14"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="2"/>
@@ -11452,7 +11443,7 @@
       <c r="Z187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="15"/>
+      <c r="A188" s="14"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="2"/>
@@ -11480,7 +11471,7 @@
       <c r="Z188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="15"/>
+      <c r="A189" s="14"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="2"/>
@@ -11508,7 +11499,7 @@
       <c r="Z189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="15"/>
+      <c r="A190" s="14"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="2"/>
@@ -11536,7 +11527,7 @@
       <c r="Z190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="15"/>
+      <c r="A191" s="14"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="2"/>
@@ -11564,7 +11555,7 @@
       <c r="Z191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="15"/>
+      <c r="A192" s="14"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="2"/>
@@ -11592,7 +11583,7 @@
       <c r="Z192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="15"/>
+      <c r="A193" s="14"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="2"/>
@@ -11620,7 +11611,7 @@
       <c r="Z193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="15"/>
+      <c r="A194" s="14"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="2"/>
@@ -11648,7 +11639,7 @@
       <c r="Z194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="15"/>
+      <c r="A195" s="14"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="2"/>
@@ -11676,7 +11667,7 @@
       <c r="Z195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="15"/>
+      <c r="A196" s="14"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="2"/>
@@ -11704,7 +11695,7 @@
       <c r="Z196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="15"/>
+      <c r="A197" s="14"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="2"/>
@@ -11732,7 +11723,7 @@
       <c r="Z197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="15"/>
+      <c r="A198" s="14"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="2"/>
@@ -11760,7 +11751,7 @@
       <c r="Z198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="15"/>
+      <c r="A199" s="14"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="2"/>
@@ -11788,7 +11779,7 @@
       <c r="Z199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="15"/>
+      <c r="A200" s="14"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="2"/>
@@ -11816,7 +11807,7 @@
       <c r="Z200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="15"/>
+      <c r="A201" s="14"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="2"/>
@@ -11844,7 +11835,7 @@
       <c r="Z201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="15"/>
+      <c r="A202" s="14"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
       <c r="D202" s="2"/>
@@ -11872,7 +11863,7 @@
       <c r="Z202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="15"/>
+      <c r="A203" s="14"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="2"/>
@@ -11900,7 +11891,7 @@
       <c r="Z203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="15"/>
+      <c r="A204" s="14"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="2"/>
@@ -11928,7 +11919,7 @@
       <c r="Z204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="15"/>
+      <c r="A205" s="14"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="2"/>
@@ -11956,7 +11947,7 @@
       <c r="Z205" s="3"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="15"/>
+      <c r="A206" s="14"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="2"/>
@@ -11984,7 +11975,7 @@
       <c r="Z206" s="3"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="15"/>
+      <c r="A207" s="14"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="2"/>
@@ -12012,7 +12003,7 @@
       <c r="Z207" s="3"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="15"/>
+      <c r="A208" s="14"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
       <c r="D208" s="2"/>
@@ -12040,7 +12031,7 @@
       <c r="Z208" s="3"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="15"/>
+      <c r="A209" s="14"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="2"/>
@@ -12068,7 +12059,7 @@
       <c r="Z209" s="3"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="15"/>
+      <c r="A210" s="14"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
       <c r="D210" s="2"/>
@@ -12096,7 +12087,7 @@
       <c r="Z210" s="3"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="15"/>
+      <c r="A211" s="14"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="2"/>
@@ -12124,7 +12115,7 @@
       <c r="Z211" s="3"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="15"/>
+      <c r="A212" s="14"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
       <c r="D212" s="2"/>
@@ -12152,7 +12143,7 @@
       <c r="Z212" s="3"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="15"/>
+      <c r="A213" s="14"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
       <c r="D213" s="2"/>
@@ -12180,7 +12171,7 @@
       <c r="Z213" s="3"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="15"/>
+      <c r="A214" s="14"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
       <c r="D214" s="2"/>
@@ -12208,7 +12199,7 @@
       <c r="Z214" s="3"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="15"/>
+      <c r="A215" s="14"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="2"/>
@@ -12236,7 +12227,7 @@
       <c r="Z215" s="3"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="15"/>
+      <c r="A216" s="14"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="2"/>
@@ -12264,7 +12255,7 @@
       <c r="Z216" s="3"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="15"/>
+      <c r="A217" s="14"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="2"/>
@@ -12292,7 +12283,7 @@
       <c r="Z217" s="3"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="15"/>
+      <c r="A218" s="14"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
       <c r="D218" s="2"/>
@@ -12320,7 +12311,7 @@
       <c r="Z218" s="3"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="15"/>
+      <c r="A219" s="14"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
       <c r="D219" s="2"/>
@@ -12348,7 +12339,7 @@
       <c r="Z219" s="3"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="15"/>
+      <c r="A220" s="14"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
       <c r="D220" s="2"/>
@@ -12376,7 +12367,7 @@
       <c r="Z220" s="3"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="15"/>
+      <c r="A221" s="14"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="2"/>
@@ -12404,7 +12395,7 @@
       <c r="Z221" s="3"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="15"/>
+      <c r="A222" s="14"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
       <c r="D222" s="2"/>
@@ -12432,7 +12423,7 @@
       <c r="Z222" s="3"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="15"/>
+      <c r="A223" s="14"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="2"/>
@@ -12460,7 +12451,7 @@
       <c r="Z223" s="3"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="15"/>
+      <c r="A224" s="14"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
       <c r="D224" s="2"/>
@@ -12488,7 +12479,7 @@
       <c r="Z224" s="3"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="15"/>
+      <c r="A225" s="14"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="2"/>
@@ -12516,7 +12507,7 @@
       <c r="Z225" s="3"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="15"/>
+      <c r="A226" s="14"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
       <c r="D226" s="2"/>
@@ -12544,7 +12535,7 @@
       <c r="Z226" s="3"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="15"/>
+      <c r="A227" s="14"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="2"/>
@@ -12572,7 +12563,7 @@
       <c r="Z227" s="3"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="15"/>
+      <c r="A228" s="14"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
       <c r="D228" s="2"/>
@@ -12600,7 +12591,7 @@
       <c r="Z228" s="3"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="15"/>
+      <c r="A229" s="14"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="2"/>
@@ -12628,7 +12619,7 @@
       <c r="Z229" s="3"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="15"/>
+      <c r="A230" s="14"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
       <c r="D230" s="2"/>
@@ -12656,7 +12647,7 @@
       <c r="Z230" s="3"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="15"/>
+      <c r="A231" s="14"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
       <c r="D231" s="2"/>
@@ -12684,7 +12675,7 @@
       <c r="Z231" s="3"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="15"/>
+      <c r="A232" s="14"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
       <c r="D232" s="2"/>
@@ -12712,7 +12703,7 @@
       <c r="Z232" s="3"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="15"/>
+      <c r="A233" s="14"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="2"/>
@@ -12740,7 +12731,7 @@
       <c r="Z233" s="3"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="15"/>
+      <c r="A234" s="14"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="2"/>
@@ -12768,7 +12759,7 @@
       <c r="Z234" s="3"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="15"/>
+      <c r="A235" s="14"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="2"/>
@@ -12796,7 +12787,7 @@
       <c r="Z235" s="3"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="15"/>
+      <c r="A236" s="14"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="2"/>
@@ -12824,7 +12815,7 @@
       <c r="Z236" s="3"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="15"/>
+      <c r="A237" s="14"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="2"/>
@@ -12852,7 +12843,7 @@
       <c r="Z237" s="3"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="15"/>
+      <c r="A238" s="14"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
       <c r="D238" s="2"/>
@@ -12880,7 +12871,7 @@
       <c r="Z238" s="3"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="15"/>
+      <c r="A239" s="14"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
       <c r="D239" s="2"/>
@@ -12908,7 +12899,7 @@
       <c r="Z239" s="3"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="15"/>
+      <c r="A240" s="14"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
       <c r="D240" s="2"/>
@@ -12936,7 +12927,7 @@
       <c r="Z240" s="3"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="15"/>
+      <c r="A241" s="14"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
       <c r="D241" s="2"/>
@@ -12964,7 +12955,7 @@
       <c r="Z241" s="3"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="15"/>
+      <c r="A242" s="14"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
       <c r="D242" s="2"/>
@@ -12992,7 +12983,7 @@
       <c r="Z242" s="3"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="15"/>
+      <c r="A243" s="14"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
       <c r="D243" s="2"/>
@@ -13020,7 +13011,7 @@
       <c r="Z243" s="3"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="15"/>
+      <c r="A244" s="14"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
       <c r="D244" s="2"/>
@@ -13048,7 +13039,7 @@
       <c r="Z244" s="3"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="15"/>
+      <c r="A245" s="14"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
       <c r="D245" s="2"/>
@@ -13076,7 +13067,7 @@
       <c r="Z245" s="3"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="15"/>
+      <c r="A246" s="14"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
       <c r="D246" s="2"/>
@@ -13104,7 +13095,7 @@
       <c r="Z246" s="3"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="15"/>
+      <c r="A247" s="14"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
       <c r="D247" s="2"/>
@@ -13132,7 +13123,7 @@
       <c r="Z247" s="3"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="15"/>
+      <c r="A248" s="14"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
       <c r="D248" s="2"/>
@@ -13160,7 +13151,7 @@
       <c r="Z248" s="3"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="15"/>
+      <c r="A249" s="14"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
       <c r="D249" s="2"/>
@@ -13188,7 +13179,7 @@
       <c r="Z249" s="3"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="15"/>
+      <c r="A250" s="14"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
       <c r="D250" s="2"/>
@@ -13216,7 +13207,7 @@
       <c r="Z250" s="3"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="15"/>
+      <c r="A251" s="14"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
       <c r="D251" s="2"/>
@@ -13244,7 +13235,7 @@
       <c r="Z251" s="3"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="15"/>
+      <c r="A252" s="14"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
       <c r="D252" s="2"/>
@@ -13272,7 +13263,7 @@
       <c r="Z252" s="3"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="15"/>
+      <c r="A253" s="14"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
       <c r="D253" s="2"/>
@@ -13300,7 +13291,7 @@
       <c r="Z253" s="3"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="15"/>
+      <c r="A254" s="14"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
       <c r="D254" s="2"/>
@@ -13328,7 +13319,7 @@
       <c r="Z254" s="3"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="15"/>
+      <c r="A255" s="14"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
       <c r="D255" s="2"/>
@@ -13356,7 +13347,7 @@
       <c r="Z255" s="3"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="15"/>
+      <c r="A256" s="14"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
       <c r="D256" s="2"/>
@@ -13384,7 +13375,7 @@
       <c r="Z256" s="3"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="15"/>
+      <c r="A257" s="14"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
       <c r="D257" s="2"/>
@@ -13412,7 +13403,7 @@
       <c r="Z257" s="3"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="15"/>
+      <c r="A258" s="14"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
       <c r="D258" s="2"/>
@@ -13440,7 +13431,7 @@
       <c r="Z258" s="3"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="15"/>
+      <c r="A259" s="14"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
       <c r="D259" s="2"/>
@@ -13468,7 +13459,7 @@
       <c r="Z259" s="3"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="15"/>
+      <c r="A260" s="14"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
       <c r="D260" s="2"/>
@@ -13496,7 +13487,7 @@
       <c r="Z260" s="3"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="15"/>
+      <c r="A261" s="14"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
       <c r="D261" s="2"/>
@@ -13524,7 +13515,7 @@
       <c r="Z261" s="3"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="15"/>
+      <c r="A262" s="14"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
       <c r="D262" s="2"/>
@@ -13552,7 +13543,7 @@
       <c r="Z262" s="3"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="15"/>
+      <c r="A263" s="14"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
       <c r="D263" s="2"/>
@@ -13580,7 +13571,7 @@
       <c r="Z263" s="3"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="15"/>
+      <c r="A264" s="14"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
       <c r="D264" s="2"/>
@@ -13608,7 +13599,7 @@
       <c r="Z264" s="3"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="15"/>
+      <c r="A265" s="14"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
       <c r="D265" s="2"/>
@@ -13636,7 +13627,7 @@
       <c r="Z265" s="3"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="15"/>
+      <c r="A266" s="14"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
       <c r="D266" s="2"/>
@@ -13664,7 +13655,7 @@
       <c r="Z266" s="3"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="15"/>
+      <c r="A267" s="14"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
       <c r="D267" s="2"/>
@@ -13692,7 +13683,7 @@
       <c r="Z267" s="3"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="15"/>
+      <c r="A268" s="14"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
       <c r="D268" s="2"/>
@@ -13720,7 +13711,7 @@
       <c r="Z268" s="3"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="15"/>
+      <c r="A269" s="14"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
       <c r="D269" s="2"/>
@@ -13748,7 +13739,7 @@
       <c r="Z269" s="3"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="15"/>
+      <c r="A270" s="14"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
       <c r="D270" s="2"/>
@@ -13776,7 +13767,7 @@
       <c r="Z270" s="3"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="15"/>
+      <c r="A271" s="14"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
       <c r="D271" s="2"/>
@@ -13804,7 +13795,7 @@
       <c r="Z271" s="3"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="15"/>
+      <c r="A272" s="14"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
       <c r="D272" s="2"/>
@@ -13832,7 +13823,7 @@
       <c r="Z272" s="3"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="15"/>
+      <c r="A273" s="14"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
       <c r="D273" s="2"/>
@@ -13860,7 +13851,7 @@
       <c r="Z273" s="3"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="15"/>
+      <c r="A274" s="14"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
       <c r="D274" s="2"/>
@@ -13888,7 +13879,7 @@
       <c r="Z274" s="3"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="15"/>
+      <c r="A275" s="14"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
       <c r="D275" s="2"/>
@@ -13916,7 +13907,7 @@
       <c r="Z275" s="3"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="15"/>
+      <c r="A276" s="14"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
       <c r="D276" s="2"/>
@@ -13944,7 +13935,7 @@
       <c r="Z276" s="3"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="15"/>
+      <c r="A277" s="14"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
       <c r="D277" s="2"/>
@@ -13972,7 +13963,7 @@
       <c r="Z277" s="3"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="15"/>
+      <c r="A278" s="14"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
       <c r="D278" s="2"/>
@@ -14000,7 +13991,7 @@
       <c r="Z278" s="3"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="15"/>
+      <c r="A279" s="14"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
       <c r="D279" s="2"/>
@@ -14028,7 +14019,7 @@
       <c r="Z279" s="3"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="15"/>
+      <c r="A280" s="14"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
       <c r="D280" s="2"/>
@@ -14056,7 +14047,7 @@
       <c r="Z280" s="3"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="15"/>
+      <c r="A281" s="14"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
       <c r="D281" s="2"/>
@@ -14084,7 +14075,7 @@
       <c r="Z281" s="3"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="15"/>
+      <c r="A282" s="14"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
       <c r="D282" s="2"/>
@@ -14112,7 +14103,7 @@
       <c r="Z282" s="3"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="15"/>
+      <c r="A283" s="14"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
       <c r="D283" s="2"/>
@@ -14140,7 +14131,7 @@
       <c r="Z283" s="3"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="15"/>
+      <c r="A284" s="14"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
       <c r="D284" s="2"/>
@@ -14168,7 +14159,7 @@
       <c r="Z284" s="3"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="15"/>
+      <c r="A285" s="14"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
       <c r="D285" s="2"/>
@@ -14196,7 +14187,7 @@
       <c r="Z285" s="3"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="15"/>
+      <c r="A286" s="14"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
       <c r="D286" s="2"/>
@@ -14224,7 +14215,7 @@
       <c r="Z286" s="3"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="15"/>
+      <c r="A287" s="14"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
       <c r="D287" s="2"/>
@@ -14252,7 +14243,7 @@
       <c r="Z287" s="3"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="15"/>
+      <c r="A288" s="14"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
       <c r="D288" s="2"/>
@@ -14280,7 +14271,7 @@
       <c r="Z288" s="3"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="15"/>
+      <c r="A289" s="14"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
       <c r="D289" s="2"/>
@@ -14308,7 +14299,7 @@
       <c r="Z289" s="3"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="15"/>
+      <c r="A290" s="14"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
       <c r="D290" s="2"/>
@@ -14336,7 +14327,7 @@
       <c r="Z290" s="3"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="15"/>
+      <c r="A291" s="14"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
       <c r="D291" s="2"/>
@@ -14364,7 +14355,7 @@
       <c r="Z291" s="3"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="15"/>
+      <c r="A292" s="14"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
       <c r="D292" s="2"/>
@@ -14392,7 +14383,7 @@
       <c r="Z292" s="3"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="15"/>
+      <c r="A293" s="14"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
       <c r="D293" s="2"/>
@@ -14420,7 +14411,7 @@
       <c r="Z293" s="3"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="15"/>
+      <c r="A294" s="14"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
       <c r="D294" s="2"/>
@@ -14448,7 +14439,7 @@
       <c r="Z294" s="3"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="15"/>
+      <c r="A295" s="14"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
       <c r="D295" s="2"/>
@@ -14476,7 +14467,7 @@
       <c r="Z295" s="3"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="15"/>
+      <c r="A296" s="14"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
       <c r="D296" s="2"/>
@@ -14504,7 +14495,7 @@
       <c r="Z296" s="3"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="15"/>
+      <c r="A297" s="14"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
       <c r="D297" s="2"/>
@@ -14532,7 +14523,7 @@
       <c r="Z297" s="3"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="15"/>
+      <c r="A298" s="14"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
       <c r="D298" s="2"/>
@@ -14560,7 +14551,7 @@
       <c r="Z298" s="3"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="15"/>
+      <c r="A299" s="14"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
       <c r="D299" s="2"/>
@@ -14588,7 +14579,7 @@
       <c r="Z299" s="3"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="15"/>
+      <c r="A300" s="14"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
       <c r="D300" s="2"/>
@@ -14616,7 +14607,7 @@
       <c r="Z300" s="3"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="15"/>
+      <c r="A301" s="14"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
       <c r="D301" s="2"/>
@@ -14644,7 +14635,7 @@
       <c r="Z301" s="3"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="15"/>
+      <c r="A302" s="14"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
       <c r="D302" s="2"/>
@@ -14672,7 +14663,7 @@
       <c r="Z302" s="3"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="15"/>
+      <c r="A303" s="14"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
       <c r="D303" s="2"/>
@@ -14700,7 +14691,7 @@
       <c r="Z303" s="3"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="15"/>
+      <c r="A304" s="14"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
       <c r="D304" s="2"/>
@@ -14728,7 +14719,7 @@
       <c r="Z304" s="3"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="15"/>
+      <c r="A305" s="14"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
       <c r="D305" s="2"/>
@@ -14756,7 +14747,7 @@
       <c r="Z305" s="3"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="15"/>
+      <c r="A306" s="14"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
       <c r="D306" s="2"/>
@@ -14784,7 +14775,7 @@
       <c r="Z306" s="3"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="15"/>
+      <c r="A307" s="14"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
       <c r="D307" s="2"/>
@@ -14812,7 +14803,7 @@
       <c r="Z307" s="3"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="15"/>
+      <c r="A308" s="14"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
       <c r="D308" s="2"/>
@@ -14840,7 +14831,7 @@
       <c r="Z308" s="3"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="15"/>
+      <c r="A309" s="14"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
       <c r="D309" s="2"/>
@@ -14868,7 +14859,7 @@
       <c r="Z309" s="3"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="15"/>
+      <c r="A310" s="14"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
       <c r="D310" s="2"/>
@@ -14896,7 +14887,7 @@
       <c r="Z310" s="3"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="15"/>
+      <c r="A311" s="14"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
       <c r="D311" s="2"/>
@@ -14924,7 +14915,7 @@
       <c r="Z311" s="3"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="15"/>
+      <c r="A312" s="14"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
       <c r="D312" s="2"/>
@@ -14952,7 +14943,7 @@
       <c r="Z312" s="3"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="15"/>
+      <c r="A313" s="14"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
       <c r="D313" s="2"/>
@@ -14980,7 +14971,7 @@
       <c r="Z313" s="3"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="15"/>
+      <c r="A314" s="14"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
       <c r="D314" s="2"/>
@@ -15008,7 +14999,7 @@
       <c r="Z314" s="3"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="15"/>
+      <c r="A315" s="14"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
       <c r="D315" s="2"/>
@@ -15036,7 +15027,7 @@
       <c r="Z315" s="3"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="15"/>
+      <c r="A316" s="14"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
       <c r="D316" s="2"/>
@@ -15064,7 +15055,7 @@
       <c r="Z316" s="3"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="15"/>
+      <c r="A317" s="14"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
       <c r="D317" s="2"/>
@@ -15092,7 +15083,7 @@
       <c r="Z317" s="3"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="15"/>
+      <c r="A318" s="14"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
       <c r="D318" s="2"/>
@@ -15120,7 +15111,7 @@
       <c r="Z318" s="3"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="15"/>
+      <c r="A319" s="14"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
       <c r="D319" s="2"/>
@@ -15148,7 +15139,7 @@
       <c r="Z319" s="3"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="15"/>
+      <c r="A320" s="14"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
       <c r="D320" s="2"/>
@@ -15176,7 +15167,7 @@
       <c r="Z320" s="3"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="15"/>
+      <c r="A321" s="14"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
       <c r="D321" s="2"/>
@@ -15204,7 +15195,7 @@
       <c r="Z321" s="3"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="15"/>
+      <c r="A322" s="14"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
       <c r="D322" s="2"/>
@@ -15232,7 +15223,7 @@
       <c r="Z322" s="3"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="15"/>
+      <c r="A323" s="14"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
       <c r="D323" s="2"/>
@@ -15260,7 +15251,7 @@
       <c r="Z323" s="3"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="15"/>
+      <c r="A324" s="14"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
       <c r="D324" s="2"/>
@@ -15288,7 +15279,7 @@
       <c r="Z324" s="3"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="15"/>
+      <c r="A325" s="14"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
       <c r="D325" s="2"/>
@@ -15316,7 +15307,7 @@
       <c r="Z325" s="3"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="15"/>
+      <c r="A326" s="14"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
       <c r="D326" s="2"/>
@@ -15344,7 +15335,7 @@
       <c r="Z326" s="3"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="15"/>
+      <c r="A327" s="14"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
       <c r="D327" s="2"/>
@@ -15372,7 +15363,7 @@
       <c r="Z327" s="3"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="15"/>
+      <c r="A328" s="14"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
       <c r="D328" s="2"/>
@@ -15400,7 +15391,7 @@
       <c r="Z328" s="3"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="15"/>
+      <c r="A329" s="14"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
       <c r="D329" s="2"/>
@@ -15428,7 +15419,7 @@
       <c r="Z329" s="3"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="15"/>
+      <c r="A330" s="14"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
       <c r="D330" s="2"/>
@@ -15456,7 +15447,7 @@
       <c r="Z330" s="3"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="15"/>
+      <c r="A331" s="14"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
       <c r="D331" s="2"/>
@@ -15484,7 +15475,7 @@
       <c r="Z331" s="3"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="15"/>
+      <c r="A332" s="14"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
       <c r="D332" s="2"/>
@@ -15512,7 +15503,7 @@
       <c r="Z332" s="3"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="15"/>
+      <c r="A333" s="14"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
       <c r="D333" s="2"/>
@@ -15540,7 +15531,7 @@
       <c r="Z333" s="3"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="15"/>
+      <c r="A334" s="14"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
       <c r="D334" s="2"/>
@@ -15568,7 +15559,7 @@
       <c r="Z334" s="3"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="15"/>
+      <c r="A335" s="14"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
       <c r="D335" s="2"/>
@@ -15596,7 +15587,7 @@
       <c r="Z335" s="3"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="15"/>
+      <c r="A336" s="14"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
       <c r="D336" s="2"/>
@@ -15624,7 +15615,7 @@
       <c r="Z336" s="3"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="15"/>
+      <c r="A337" s="14"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
       <c r="D337" s="2"/>
@@ -15652,7 +15643,7 @@
       <c r="Z337" s="3"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="15"/>
+      <c r="A338" s="14"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
       <c r="D338" s="2"/>
@@ -15680,7 +15671,7 @@
       <c r="Z338" s="3"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="15"/>
+      <c r="A339" s="14"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
       <c r="D339" s="2"/>
@@ -15708,7 +15699,7 @@
       <c r="Z339" s="3"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="15"/>
+      <c r="A340" s="14"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
       <c r="D340" s="2"/>
@@ -15736,7 +15727,7 @@
       <c r="Z340" s="3"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="15"/>
+      <c r="A341" s="14"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
       <c r="D341" s="2"/>
@@ -15764,7 +15755,7 @@
       <c r="Z341" s="3"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="15"/>
+      <c r="A342" s="14"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
       <c r="D342" s="2"/>
@@ -15792,7 +15783,7 @@
       <c r="Z342" s="3"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="15"/>
+      <c r="A343" s="14"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
       <c r="D343" s="2"/>
@@ -15820,7 +15811,7 @@
       <c r="Z343" s="3"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="15"/>
+      <c r="A344" s="14"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
       <c r="D344" s="2"/>
@@ -15848,7 +15839,7 @@
       <c r="Z344" s="3"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="15"/>
+      <c r="A345" s="14"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
       <c r="D345" s="2"/>
@@ -15876,7 +15867,7 @@
       <c r="Z345" s="3"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="15"/>
+      <c r="A346" s="14"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
       <c r="D346" s="2"/>
@@ -15904,7 +15895,7 @@
       <c r="Z346" s="3"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="15"/>
+      <c r="A347" s="14"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
       <c r="D347" s="2"/>
@@ -15932,7 +15923,7 @@
       <c r="Z347" s="3"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="15"/>
+      <c r="A348" s="14"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
       <c r="D348" s="2"/>
@@ -15960,7 +15951,7 @@
       <c r="Z348" s="3"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="15"/>
+      <c r="A349" s="14"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
       <c r="D349" s="2"/>
@@ -15988,7 +15979,7 @@
       <c r="Z349" s="3"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="15"/>
+      <c r="A350" s="14"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
       <c r="D350" s="2"/>
@@ -16016,7 +16007,7 @@
       <c r="Z350" s="3"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="15"/>
+      <c r="A351" s="14"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
       <c r="D351" s="2"/>
@@ -16044,7 +16035,7 @@
       <c r="Z351" s="3"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="15"/>
+      <c r="A352" s="14"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
       <c r="D352" s="2"/>
@@ -16072,7 +16063,7 @@
       <c r="Z352" s="3"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="15"/>
+      <c r="A353" s="14"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
       <c r="D353" s="2"/>
@@ -16100,7 +16091,7 @@
       <c r="Z353" s="3"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="15"/>
+      <c r="A354" s="14"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
       <c r="D354" s="2"/>
@@ -16128,7 +16119,7 @@
       <c r="Z354" s="3"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="15"/>
+      <c r="A355" s="14"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
       <c r="D355" s="2"/>
@@ -16156,7 +16147,7 @@
       <c r="Z355" s="3"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="15"/>
+      <c r="A356" s="14"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
       <c r="D356" s="2"/>
@@ -16184,7 +16175,7 @@
       <c r="Z356" s="3"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="15"/>
+      <c r="A357" s="14"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
       <c r="D357" s="2"/>
@@ -16212,7 +16203,7 @@
       <c r="Z357" s="3"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="15"/>
+      <c r="A358" s="14"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
       <c r="D358" s="2"/>
@@ -16240,7 +16231,7 @@
       <c r="Z358" s="3"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="15"/>
+      <c r="A359" s="14"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
       <c r="D359" s="2"/>
@@ -16268,7 +16259,7 @@
       <c r="Z359" s="3"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="15"/>
+      <c r="A360" s="14"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
       <c r="D360" s="2"/>
@@ -16296,7 +16287,7 @@
       <c r="Z360" s="3"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="15"/>
+      <c r="A361" s="14"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
       <c r="D361" s="2"/>
@@ -16324,7 +16315,7 @@
       <c r="Z361" s="3"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="15"/>
+      <c r="A362" s="14"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
       <c r="D362" s="2"/>
@@ -16352,7 +16343,7 @@
       <c r="Z362" s="3"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="15"/>
+      <c r="A363" s="14"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
       <c r="D363" s="2"/>
@@ -16380,7 +16371,7 @@
       <c r="Z363" s="3"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="15"/>
+      <c r="A364" s="14"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
       <c r="D364" s="2"/>
@@ -16408,7 +16399,7 @@
       <c r="Z364" s="3"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="15"/>
+      <c r="A365" s="14"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
       <c r="D365" s="2"/>
@@ -16436,7 +16427,7 @@
       <c r="Z365" s="3"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="15"/>
+      <c r="A366" s="14"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
       <c r="D366" s="2"/>
@@ -16464,7 +16455,7 @@
       <c r="Z366" s="3"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="15"/>
+      <c r="A367" s="14"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
       <c r="D367" s="2"/>
@@ -16492,7 +16483,7 @@
       <c r="Z367" s="3"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="15"/>
+      <c r="A368" s="14"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
       <c r="D368" s="2"/>
@@ -16520,7 +16511,7 @@
       <c r="Z368" s="3"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="15"/>
+      <c r="A369" s="14"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
       <c r="D369" s="2"/>
@@ -16548,7 +16539,7 @@
       <c r="Z369" s="3"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="15"/>
+      <c r="A370" s="14"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
       <c r="D370" s="2"/>
@@ -16576,7 +16567,7 @@
       <c r="Z370" s="3"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="15"/>
+      <c r="A371" s="14"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
       <c r="D371" s="2"/>
@@ -16604,7 +16595,7 @@
       <c r="Z371" s="3"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="15"/>
+      <c r="A372" s="14"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
       <c r="D372" s="2"/>
@@ -16632,7 +16623,7 @@
       <c r="Z372" s="3"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="15"/>
+      <c r="A373" s="14"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
       <c r="D373" s="2"/>
@@ -16660,7 +16651,7 @@
       <c r="Z373" s="3"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="15"/>
+      <c r="A374" s="14"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
       <c r="D374" s="2"/>
@@ -16688,7 +16679,7 @@
       <c r="Z374" s="3"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="15"/>
+      <c r="A375" s="14"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
       <c r="D375" s="2"/>
@@ -16716,7 +16707,7 @@
       <c r="Z375" s="3"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="15"/>
+      <c r="A376" s="14"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
       <c r="D376" s="2"/>
@@ -16744,7 +16735,7 @@
       <c r="Z376" s="3"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="15"/>
+      <c r="A377" s="14"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
       <c r="D377" s="2"/>
@@ -16772,7 +16763,7 @@
       <c r="Z377" s="3"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="15"/>
+      <c r="A378" s="14"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
       <c r="D378" s="2"/>
@@ -16800,7 +16791,7 @@
       <c r="Z378" s="3"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="15"/>
+      <c r="A379" s="14"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
       <c r="D379" s="2"/>
@@ -16828,7 +16819,7 @@
       <c r="Z379" s="3"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="15"/>
+      <c r="A380" s="14"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
       <c r="D380" s="2"/>
@@ -16856,7 +16847,7 @@
       <c r="Z380" s="3"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="15"/>
+      <c r="A381" s="14"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
       <c r="D381" s="2"/>
@@ -16884,7 +16875,7 @@
       <c r="Z381" s="3"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="15"/>
+      <c r="A382" s="14"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
       <c r="D382" s="2"/>
@@ -16912,7 +16903,7 @@
       <c r="Z382" s="3"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="15"/>
+      <c r="A383" s="14"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
       <c r="D383" s="2"/>
@@ -16940,7 +16931,7 @@
       <c r="Z383" s="3"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="15"/>
+      <c r="A384" s="14"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
       <c r="D384" s="2"/>
@@ -16968,7 +16959,7 @@
       <c r="Z384" s="3"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="15"/>
+      <c r="A385" s="14"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
       <c r="D385" s="2"/>
@@ -16996,7 +16987,7 @@
       <c r="Z385" s="3"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="15"/>
+      <c r="A386" s="14"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
       <c r="D386" s="2"/>
@@ -17024,7 +17015,7 @@
       <c r="Z386" s="3"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="15"/>
+      <c r="A387" s="14"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
       <c r="D387" s="2"/>
@@ -17052,7 +17043,7 @@
       <c r="Z387" s="3"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="15"/>
+      <c r="A388" s="14"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
       <c r="D388" s="2"/>
@@ -17080,7 +17071,7 @@
       <c r="Z388" s="3"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="15"/>
+      <c r="A389" s="14"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
       <c r="D389" s="2"/>
@@ -17108,7 +17099,7 @@
       <c r="Z389" s="3"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="15"/>
+      <c r="A390" s="14"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
       <c r="D390" s="2"/>
@@ -17136,7 +17127,7 @@
       <c r="Z390" s="3"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="15"/>
+      <c r="A391" s="14"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
       <c r="D391" s="2"/>
@@ -17164,7 +17155,7 @@
       <c r="Z391" s="3"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="15"/>
+      <c r="A392" s="14"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
       <c r="D392" s="2"/>
@@ -17192,7 +17183,7 @@
       <c r="Z392" s="3"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="15"/>
+      <c r="A393" s="14"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
       <c r="D393" s="2"/>
@@ -17220,7 +17211,7 @@
       <c r="Z393" s="3"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="15"/>
+      <c r="A394" s="14"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
       <c r="D394" s="2"/>
@@ -17248,7 +17239,7 @@
       <c r="Z394" s="3"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="15"/>
+      <c r="A395" s="14"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
       <c r="D395" s="2"/>
@@ -17276,7 +17267,7 @@
       <c r="Z395" s="3"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="15"/>
+      <c r="A396" s="14"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
       <c r="D396" s="2"/>
@@ -17304,7 +17295,7 @@
       <c r="Z396" s="3"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="15"/>
+      <c r="A397" s="14"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
       <c r="D397" s="2"/>
@@ -17332,7 +17323,7 @@
       <c r="Z397" s="3"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="15"/>
+      <c r="A398" s="14"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
       <c r="D398" s="2"/>
@@ -17360,7 +17351,7 @@
       <c r="Z398" s="3"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="15"/>
+      <c r="A399" s="14"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
       <c r="D399" s="2"/>
@@ -17388,7 +17379,7 @@
       <c r="Z399" s="3"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="15"/>
+      <c r="A400" s="14"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
       <c r="D400" s="2"/>
@@ -17416,7 +17407,7 @@
       <c r="Z400" s="3"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="15"/>
+      <c r="A401" s="14"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
       <c r="D401" s="2"/>
@@ -17444,7 +17435,7 @@
       <c r="Z401" s="3"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="15"/>
+      <c r="A402" s="14"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
       <c r="D402" s="2"/>
@@ -17472,7 +17463,7 @@
       <c r="Z402" s="3"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="15"/>
+      <c r="A403" s="14"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
       <c r="D403" s="2"/>
@@ -17500,7 +17491,7 @@
       <c r="Z403" s="3"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="15"/>
+      <c r="A404" s="14"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
       <c r="D404" s="2"/>
@@ -17528,7 +17519,7 @@
       <c r="Z404" s="3"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="15"/>
+      <c r="A405" s="14"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
       <c r="D405" s="2"/>
@@ -17556,7 +17547,7 @@
       <c r="Z405" s="3"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="15"/>
+      <c r="A406" s="14"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
       <c r="D406" s="2"/>
@@ -17584,7 +17575,7 @@
       <c r="Z406" s="3"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="15"/>
+      <c r="A407" s="14"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
       <c r="D407" s="2"/>
@@ -17612,7 +17603,7 @@
       <c r="Z407" s="3"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="15"/>
+      <c r="A408" s="14"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
       <c r="D408" s="2"/>
@@ -17640,7 +17631,7 @@
       <c r="Z408" s="3"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="15"/>
+      <c r="A409" s="14"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
       <c r="D409" s="2"/>
@@ -17668,7 +17659,7 @@
       <c r="Z409" s="3"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="15"/>
+      <c r="A410" s="14"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
       <c r="D410" s="2"/>
@@ -17696,7 +17687,7 @@
       <c r="Z410" s="3"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="15"/>
+      <c r="A411" s="14"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
       <c r="D411" s="2"/>
@@ -17724,7 +17715,7 @@
       <c r="Z411" s="3"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="15"/>
+      <c r="A412" s="14"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
       <c r="D412" s="2"/>
@@ -17752,7 +17743,7 @@
       <c r="Z412" s="3"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="15"/>
+      <c r="A413" s="14"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
       <c r="D413" s="2"/>
@@ -17780,7 +17771,7 @@
       <c r="Z413" s="3"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="15"/>
+      <c r="A414" s="14"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
       <c r="D414" s="2"/>
@@ -17808,7 +17799,7 @@
       <c r="Z414" s="3"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="15"/>
+      <c r="A415" s="14"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
       <c r="D415" s="2"/>
@@ -17836,7 +17827,7 @@
       <c r="Z415" s="3"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="15"/>
+      <c r="A416" s="14"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
       <c r="D416" s="2"/>
@@ -17864,7 +17855,7 @@
       <c r="Z416" s="3"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="15"/>
+      <c r="A417" s="14"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
       <c r="D417" s="2"/>
@@ -17892,7 +17883,7 @@
       <c r="Z417" s="3"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="15"/>
+      <c r="A418" s="14"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
       <c r="D418" s="2"/>
@@ -17920,7 +17911,7 @@
       <c r="Z418" s="3"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="15"/>
+      <c r="A419" s="14"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
       <c r="D419" s="2"/>
@@ -17948,7 +17939,7 @@
       <c r="Z419" s="3"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="15"/>
+      <c r="A420" s="14"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
       <c r="D420" s="2"/>
@@ -17976,7 +17967,7 @@
       <c r="Z420" s="3"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="15"/>
+      <c r="A421" s="14"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
       <c r="D421" s="2"/>
@@ -18004,7 +17995,7 @@
       <c r="Z421" s="3"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="15"/>
+      <c r="A422" s="14"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
       <c r="D422" s="2"/>
@@ -18032,7 +18023,7 @@
       <c r="Z422" s="3"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="15"/>
+      <c r="A423" s="14"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
       <c r="D423" s="2"/>
@@ -18060,7 +18051,7 @@
       <c r="Z423" s="3"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="15"/>
+      <c r="A424" s="14"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
       <c r="D424" s="2"/>
@@ -18088,7 +18079,7 @@
       <c r="Z424" s="3"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="15"/>
+      <c r="A425" s="14"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
       <c r="D425" s="2"/>
@@ -18116,7 +18107,7 @@
       <c r="Z425" s="3"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="15"/>
+      <c r="A426" s="14"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
       <c r="D426" s="2"/>
@@ -18144,7 +18135,7 @@
       <c r="Z426" s="3"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="15"/>
+      <c r="A427" s="14"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
       <c r="D427" s="2"/>
@@ -18172,7 +18163,7 @@
       <c r="Z427" s="3"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="15"/>
+      <c r="A428" s="14"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
       <c r="D428" s="2"/>
@@ -18200,7 +18191,7 @@
       <c r="Z428" s="3"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="15"/>
+      <c r="A429" s="14"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
       <c r="D429" s="2"/>
@@ -18228,7 +18219,7 @@
       <c r="Z429" s="3"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="15"/>
+      <c r="A430" s="14"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
       <c r="D430" s="2"/>
@@ -18256,7 +18247,7 @@
       <c r="Z430" s="3"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="15"/>
+      <c r="A431" s="14"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
       <c r="D431" s="2"/>
@@ -18284,7 +18275,7 @@
       <c r="Z431" s="3"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="15"/>
+      <c r="A432" s="14"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
       <c r="D432" s="2"/>
@@ -18312,7 +18303,7 @@
       <c r="Z432" s="3"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="15"/>
+      <c r="A433" s="14"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
       <c r="D433" s="2"/>
@@ -18340,7 +18331,7 @@
       <c r="Z433" s="3"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="15"/>
+      <c r="A434" s="14"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
       <c r="D434" s="2"/>
@@ -18368,7 +18359,7 @@
       <c r="Z434" s="3"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="15"/>
+      <c r="A435" s="14"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
       <c r="D435" s="2"/>
@@ -18396,7 +18387,7 @@
       <c r="Z435" s="3"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="15"/>
+      <c r="A436" s="14"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
       <c r="D436" s="2"/>
@@ -18424,7 +18415,7 @@
       <c r="Z436" s="3"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="15"/>
+      <c r="A437" s="14"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
       <c r="D437" s="2"/>
@@ -18452,7 +18443,7 @@
       <c r="Z437" s="3"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="15"/>
+      <c r="A438" s="14"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
       <c r="D438" s="2"/>
@@ -18480,7 +18471,7 @@
       <c r="Z438" s="3"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="15"/>
+      <c r="A439" s="14"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
       <c r="D439" s="2"/>
@@ -18508,7 +18499,7 @@
       <c r="Z439" s="3"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="15"/>
+      <c r="A440" s="14"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
       <c r="D440" s="2"/>
@@ -18536,7 +18527,7 @@
       <c r="Z440" s="3"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="15"/>
+      <c r="A441" s="14"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
       <c r="D441" s="2"/>
@@ -18564,7 +18555,7 @@
       <c r="Z441" s="3"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="15"/>
+      <c r="A442" s="14"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
       <c r="D442" s="2"/>
@@ -18592,7 +18583,7 @@
       <c r="Z442" s="3"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="15"/>
+      <c r="A443" s="14"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
       <c r="D443" s="2"/>
@@ -18620,7 +18611,7 @@
       <c r="Z443" s="3"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="15"/>
+      <c r="A444" s="14"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
       <c r="D444" s="2"/>
@@ -18648,7 +18639,7 @@
       <c r="Z444" s="3"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="15"/>
+      <c r="A445" s="14"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
       <c r="D445" s="2"/>
@@ -18676,7 +18667,7 @@
       <c r="Z445" s="3"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="15"/>
+      <c r="A446" s="14"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
       <c r="D446" s="2"/>
@@ -18704,7 +18695,7 @@
       <c r="Z446" s="3"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="15"/>
+      <c r="A447" s="14"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
       <c r="D447" s="2"/>
@@ -18732,7 +18723,7 @@
       <c r="Z447" s="3"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="15"/>
+      <c r="A448" s="14"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
       <c r="D448" s="2"/>
@@ -18760,7 +18751,7 @@
       <c r="Z448" s="3"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="15"/>
+      <c r="A449" s="14"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
       <c r="D449" s="2"/>
@@ -18788,7 +18779,7 @@
       <c r="Z449" s="3"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="15"/>
+      <c r="A450" s="14"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
       <c r="D450" s="2"/>
@@ -18816,7 +18807,7 @@
       <c r="Z450" s="3"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="15"/>
+      <c r="A451" s="14"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
       <c r="D451" s="2"/>
@@ -18844,7 +18835,7 @@
       <c r="Z451" s="3"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="15"/>
+      <c r="A452" s="14"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
       <c r="D452" s="2"/>
@@ -18872,7 +18863,7 @@
       <c r="Z452" s="3"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="15"/>
+      <c r="A453" s="14"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
       <c r="D453" s="2"/>
@@ -18900,7 +18891,7 @@
       <c r="Z453" s="3"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="15"/>
+      <c r="A454" s="14"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
       <c r="D454" s="2"/>
@@ -18928,7 +18919,7 @@
       <c r="Z454" s="3"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="15"/>
+      <c r="A455" s="14"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
       <c r="D455" s="2"/>
@@ -18956,7 +18947,7 @@
       <c r="Z455" s="3"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="15"/>
+      <c r="A456" s="14"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
       <c r="D456" s="2"/>
@@ -18984,7 +18975,7 @@
       <c r="Z456" s="3"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="15"/>
+      <c r="A457" s="14"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
       <c r="D457" s="2"/>
@@ -19012,7 +19003,7 @@
       <c r="Z457" s="3"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="15"/>
+      <c r="A458" s="14"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
       <c r="D458" s="2"/>
@@ -19040,7 +19031,7 @@
       <c r="Z458" s="3"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="15"/>
+      <c r="A459" s="14"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
       <c r="D459" s="2"/>
@@ -19068,7 +19059,7 @@
       <c r="Z459" s="3"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="15"/>
+      <c r="A460" s="14"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
       <c r="D460" s="2"/>
@@ -19096,7 +19087,7 @@
       <c r="Z460" s="3"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="15"/>
+      <c r="A461" s="14"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
       <c r="D461" s="2"/>
@@ -19124,7 +19115,7 @@
       <c r="Z461" s="3"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="15"/>
+      <c r="A462" s="14"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
       <c r="D462" s="2"/>
@@ -19152,7 +19143,7 @@
       <c r="Z462" s="3"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="15"/>
+      <c r="A463" s="14"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
       <c r="D463" s="2"/>
@@ -19180,7 +19171,7 @@
       <c r="Z463" s="3"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="15"/>
+      <c r="A464" s="14"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
       <c r="D464" s="2"/>
@@ -19208,7 +19199,7 @@
       <c r="Z464" s="3"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="15"/>
+      <c r="A465" s="14"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
       <c r="D465" s="2"/>
@@ -19236,7 +19227,7 @@
       <c r="Z465" s="3"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="15"/>
+      <c r="A466" s="14"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
       <c r="D466" s="2"/>
@@ -19264,7 +19255,7 @@
       <c r="Z466" s="3"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="15"/>
+      <c r="A467" s="14"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
       <c r="D467" s="2"/>
@@ -19292,7 +19283,7 @@
       <c r="Z467" s="3"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="15"/>
+      <c r="A468" s="14"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
       <c r="D468" s="2"/>
@@ -19320,7 +19311,7 @@
       <c r="Z468" s="3"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="15"/>
+      <c r="A469" s="14"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
       <c r="D469" s="2"/>
@@ -19348,7 +19339,7 @@
       <c r="Z469" s="3"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="15"/>
+      <c r="A470" s="14"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
       <c r="D470" s="2"/>
@@ -19376,7 +19367,7 @@
       <c r="Z470" s="3"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="15"/>
+      <c r="A471" s="14"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
       <c r="D471" s="2"/>
@@ -19404,7 +19395,7 @@
       <c r="Z471" s="3"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="15"/>
+      <c r="A472" s="14"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
       <c r="D472" s="2"/>
@@ -19432,7 +19423,7 @@
       <c r="Z472" s="3"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="15"/>
+      <c r="A473" s="14"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
       <c r="D473" s="2"/>
@@ -19460,7 +19451,7 @@
       <c r="Z473" s="3"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="15"/>
+      <c r="A474" s="14"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
       <c r="D474" s="2"/>
@@ -19488,7 +19479,7 @@
       <c r="Z474" s="3"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="15"/>
+      <c r="A475" s="14"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
       <c r="D475" s="2"/>
@@ -19516,7 +19507,7 @@
       <c r="Z475" s="3"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="15"/>
+      <c r="A476" s="14"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
       <c r="D476" s="2"/>
@@ -19544,7 +19535,7 @@
       <c r="Z476" s="3"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="15"/>
+      <c r="A477" s="14"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
       <c r="D477" s="2"/>
@@ -19572,7 +19563,7 @@
       <c r="Z477" s="3"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="15"/>
+      <c r="A478" s="14"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
       <c r="D478" s="2"/>
@@ -19600,7 +19591,7 @@
       <c r="Z478" s="3"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="15"/>
+      <c r="A479" s="14"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
       <c r="D479" s="2"/>
@@ -19628,7 +19619,7 @@
       <c r="Z479" s="3"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="15"/>
+      <c r="A480" s="14"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
       <c r="D480" s="2"/>
@@ -19656,7 +19647,7 @@
       <c r="Z480" s="3"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="15"/>
+      <c r="A481" s="14"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
       <c r="D481" s="2"/>
@@ -19684,7 +19675,7 @@
       <c r="Z481" s="3"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="15"/>
+      <c r="A482" s="14"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
       <c r="D482" s="2"/>
@@ -19712,7 +19703,7 @@
       <c r="Z482" s="3"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="15"/>
+      <c r="A483" s="14"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
       <c r="D483" s="2"/>
@@ -19740,7 +19731,7 @@
       <c r="Z483" s="3"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="15"/>
+      <c r="A484" s="14"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
       <c r="D484" s="2"/>
@@ -19768,7 +19759,7 @@
       <c r="Z484" s="3"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="15"/>
+      <c r="A485" s="14"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
       <c r="D485" s="2"/>
@@ -19796,7 +19787,7 @@
       <c r="Z485" s="3"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="15"/>
+      <c r="A486" s="14"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
       <c r="D486" s="2"/>
@@ -19824,7 +19815,7 @@
       <c r="Z486" s="3"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="15"/>
+      <c r="A487" s="14"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
       <c r="D487" s="2"/>
@@ -19852,7 +19843,7 @@
       <c r="Z487" s="3"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="15"/>
+      <c r="A488" s="14"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
       <c r="D488" s="2"/>
@@ -19880,7 +19871,7 @@
       <c r="Z488" s="3"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="15"/>
+      <c r="A489" s="14"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
       <c r="D489" s="2"/>
@@ -19908,7 +19899,7 @@
       <c r="Z489" s="3"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="15"/>
+      <c r="A490" s="14"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
       <c r="D490" s="2"/>
@@ -19936,7 +19927,7 @@
       <c r="Z490" s="3"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="15"/>
+      <c r="A491" s="14"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
       <c r="D491" s="2"/>
@@ -19964,7 +19955,7 @@
       <c r="Z491" s="3"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="15"/>
+      <c r="A492" s="14"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
       <c r="D492" s="2"/>
@@ -19992,7 +19983,7 @@
       <c r="Z492" s="3"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="15"/>
+      <c r="A493" s="14"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
       <c r="D493" s="2"/>
@@ -20020,7 +20011,7 @@
       <c r="Z493" s="3"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="15"/>
+      <c r="A494" s="14"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
       <c r="D494" s="2"/>
@@ -20048,7 +20039,7 @@
       <c r="Z494" s="3"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="15"/>
+      <c r="A495" s="14"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
       <c r="D495" s="2"/>
@@ -20076,7 +20067,7 @@
       <c r="Z495" s="3"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="15"/>
+      <c r="A496" s="14"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
       <c r="D496" s="2"/>
@@ -20104,7 +20095,7 @@
       <c r="Z496" s="3"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="15"/>
+      <c r="A497" s="14"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
       <c r="D497" s="2"/>
@@ -20132,7 +20123,7 @@
       <c r="Z497" s="3"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="15"/>
+      <c r="A498" s="14"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
       <c r="D498" s="2"/>
@@ -20160,7 +20151,7 @@
       <c r="Z498" s="3"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="15"/>
+      <c r="A499" s="14"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
       <c r="D499" s="2"/>
@@ -20188,7 +20179,7 @@
       <c r="Z499" s="3"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="15"/>
+      <c r="A500" s="14"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
       <c r="D500" s="2"/>
@@ -20216,7 +20207,7 @@
       <c r="Z500" s="3"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="15"/>
+      <c r="A501" s="14"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
       <c r="D501" s="2"/>
@@ -20244,7 +20235,7 @@
       <c r="Z501" s="3"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="15"/>
+      <c r="A502" s="14"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
       <c r="D502" s="2"/>
@@ -20272,7 +20263,7 @@
       <c r="Z502" s="3"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="15"/>
+      <c r="A503" s="14"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
       <c r="D503" s="2"/>
@@ -20300,7 +20291,7 @@
       <c r="Z503" s="3"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="15"/>
+      <c r="A504" s="14"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
       <c r="D504" s="2"/>
@@ -20328,7 +20319,7 @@
       <c r="Z504" s="3"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="15"/>
+      <c r="A505" s="14"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
       <c r="D505" s="2"/>
@@ -20356,7 +20347,7 @@
       <c r="Z505" s="3"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="15"/>
+      <c r="A506" s="14"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
       <c r="D506" s="2"/>
@@ -20384,7 +20375,7 @@
       <c r="Z506" s="3"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="15"/>
+      <c r="A507" s="14"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
       <c r="D507" s="2"/>
@@ -20412,7 +20403,7 @@
       <c r="Z507" s="3"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="15"/>
+      <c r="A508" s="14"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
       <c r="D508" s="2"/>
@@ -20440,7 +20431,7 @@
       <c r="Z508" s="3"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="15"/>
+      <c r="A509" s="14"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
       <c r="D509" s="2"/>
@@ -20468,7 +20459,7 @@
       <c r="Z509" s="3"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="15"/>
+      <c r="A510" s="14"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
       <c r="D510" s="2"/>
@@ -20496,7 +20487,7 @@
       <c r="Z510" s="3"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="15"/>
+      <c r="A511" s="14"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
       <c r="D511" s="2"/>
@@ -20524,7 +20515,7 @@
       <c r="Z511" s="3"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="15"/>
+      <c r="A512" s="14"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
       <c r="D512" s="2"/>
@@ -20552,7 +20543,7 @@
       <c r="Z512" s="3"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="15"/>
+      <c r="A513" s="14"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
       <c r="D513" s="2"/>
@@ -20580,7 +20571,7 @@
       <c r="Z513" s="3"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="15"/>
+      <c r="A514" s="14"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
       <c r="D514" s="2"/>
@@ -20608,7 +20599,7 @@
       <c r="Z514" s="3"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="15"/>
+      <c r="A515" s="14"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
       <c r="D515" s="2"/>
@@ -20636,7 +20627,7 @@
       <c r="Z515" s="3"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="15"/>
+      <c r="A516" s="14"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
       <c r="D516" s="2"/>
@@ -20664,7 +20655,7 @@
       <c r="Z516" s="3"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="15"/>
+      <c r="A517" s="14"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
       <c r="D517" s="2"/>
@@ -20692,7 +20683,7 @@
       <c r="Z517" s="3"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="15"/>
+      <c r="A518" s="14"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
       <c r="D518" s="2"/>
@@ -20720,7 +20711,7 @@
       <c r="Z518" s="3"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="15"/>
+      <c r="A519" s="14"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
       <c r="D519" s="2"/>
@@ -20748,7 +20739,7 @@
       <c r="Z519" s="3"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="15"/>
+      <c r="A520" s="14"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
       <c r="D520" s="2"/>
@@ -20776,7 +20767,7 @@
       <c r="Z520" s="3"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="15"/>
+      <c r="A521" s="14"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
       <c r="D521" s="2"/>
@@ -20804,7 +20795,7 @@
       <c r="Z521" s="3"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="15"/>
+      <c r="A522" s="14"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
       <c r="D522" s="2"/>
@@ -20832,7 +20823,7 @@
       <c r="Z522" s="3"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="15"/>
+      <c r="A523" s="14"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
       <c r="D523" s="2"/>
@@ -20860,7 +20851,7 @@
       <c r="Z523" s="3"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="15"/>
+      <c r="A524" s="14"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
       <c r="D524" s="2"/>
@@ -20888,7 +20879,7 @@
       <c r="Z524" s="3"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="15"/>
+      <c r="A525" s="14"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
       <c r="D525" s="2"/>
@@ -20916,7 +20907,7 @@
       <c r="Z525" s="3"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="15"/>
+      <c r="A526" s="14"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
       <c r="D526" s="2"/>
@@ -20944,7 +20935,7 @@
       <c r="Z526" s="3"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="15"/>
+      <c r="A527" s="14"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
       <c r="D527" s="2"/>
@@ -20972,7 +20963,7 @@
       <c r="Z527" s="3"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="15"/>
+      <c r="A528" s="14"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
       <c r="D528" s="2"/>
@@ -21000,7 +20991,7 @@
       <c r="Z528" s="3"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="15"/>
+      <c r="A529" s="14"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
       <c r="D529" s="2"/>
@@ -21028,7 +21019,7 @@
       <c r="Z529" s="3"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="15"/>
+      <c r="A530" s="14"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
       <c r="D530" s="2"/>
@@ -21056,7 +21047,7 @@
       <c r="Z530" s="3"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="15"/>
+      <c r="A531" s="14"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
       <c r="D531" s="2"/>
@@ -21084,7 +21075,7 @@
       <c r="Z531" s="3"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="15"/>
+      <c r="A532" s="14"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
       <c r="D532" s="2"/>
@@ -21112,7 +21103,7 @@
       <c r="Z532" s="3"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="15"/>
+      <c r="A533" s="14"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
       <c r="D533" s="2"/>
@@ -21140,7 +21131,7 @@
       <c r="Z533" s="3"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="15"/>
+      <c r="A534" s="14"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
       <c r="D534" s="2"/>
@@ -21168,7 +21159,7 @@
       <c r="Z534" s="3"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="15"/>
+      <c r="A535" s="14"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
       <c r="D535" s="2"/>
@@ -21196,7 +21187,7 @@
       <c r="Z535" s="3"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="15"/>
+      <c r="A536" s="14"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
       <c r="D536" s="2"/>
@@ -21224,7 +21215,7 @@
       <c r="Z536" s="3"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="15"/>
+      <c r="A537" s="14"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
       <c r="D537" s="2"/>
@@ -21252,7 +21243,7 @@
       <c r="Z537" s="3"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="15"/>
+      <c r="A538" s="14"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
       <c r="D538" s="2"/>
@@ -21280,7 +21271,7 @@
       <c r="Z538" s="3"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="15"/>
+      <c r="A539" s="14"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
       <c r="D539" s="2"/>
@@ -21308,7 +21299,7 @@
       <c r="Z539" s="3"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="15"/>
+      <c r="A540" s="14"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
       <c r="D540" s="2"/>
@@ -21336,7 +21327,7 @@
       <c r="Z540" s="3"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="15"/>
+      <c r="A541" s="14"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
       <c r="D541" s="2"/>
@@ -21364,7 +21355,7 @@
       <c r="Z541" s="3"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="15"/>
+      <c r="A542" s="14"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
       <c r="D542" s="2"/>
@@ -21392,7 +21383,7 @@
       <c r="Z542" s="3"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="15"/>
+      <c r="A543" s="14"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
       <c r="D543" s="2"/>
@@ -21420,7 +21411,7 @@
       <c r="Z543" s="3"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="15"/>
+      <c r="A544" s="14"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
       <c r="D544" s="2"/>
@@ -21448,7 +21439,7 @@
       <c r="Z544" s="3"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="15"/>
+      <c r="A545" s="14"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
       <c r="D545" s="2"/>
@@ -21476,7 +21467,7 @@
       <c r="Z545" s="3"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="15"/>
+      <c r="A546" s="14"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
       <c r="D546" s="2"/>
@@ -21504,7 +21495,7 @@
       <c r="Z546" s="3"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="15"/>
+      <c r="A547" s="14"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
       <c r="D547" s="2"/>
@@ -21532,7 +21523,7 @@
       <c r="Z547" s="3"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="15"/>
+      <c r="A548" s="14"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
       <c r="D548" s="2"/>
@@ -21560,7 +21551,7 @@
       <c r="Z548" s="3"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="15"/>
+      <c r="A549" s="14"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
       <c r="D549" s="2"/>
@@ -21588,7 +21579,7 @@
       <c r="Z549" s="3"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="15"/>
+      <c r="A550" s="14"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
       <c r="D550" s="2"/>
@@ -21616,7 +21607,7 @@
       <c r="Z550" s="3"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="15"/>
+      <c r="A551" s="14"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
       <c r="D551" s="2"/>
@@ -21644,7 +21635,7 @@
       <c r="Z551" s="3"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="15"/>
+      <c r="A552" s="14"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
       <c r="D552" s="2"/>
@@ -21672,7 +21663,7 @@
       <c r="Z552" s="3"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="15"/>
+      <c r="A553" s="14"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
       <c r="D553" s="2"/>
@@ -21700,7 +21691,7 @@
       <c r="Z553" s="3"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="15"/>
+      <c r="A554" s="14"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
       <c r="D554" s="2"/>
@@ -21728,7 +21719,7 @@
       <c r="Z554" s="3"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="15"/>
+      <c r="A555" s="14"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
       <c r="D555" s="2"/>
@@ -21756,7 +21747,7 @@
       <c r="Z555" s="3"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="15"/>
+      <c r="A556" s="14"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
       <c r="D556" s="2"/>
@@ -21784,7 +21775,7 @@
       <c r="Z556" s="3"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="15"/>
+      <c r="A557" s="14"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
       <c r="D557" s="2"/>
@@ -21812,7 +21803,7 @@
       <c r="Z557" s="3"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="15"/>
+      <c r="A558" s="14"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
       <c r="D558" s="2"/>
@@ -21840,7 +21831,7 @@
       <c r="Z558" s="3"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="15"/>
+      <c r="A559" s="14"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
       <c r="D559" s="2"/>
@@ -21868,7 +21859,7 @@
       <c r="Z559" s="3"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="15"/>
+      <c r="A560" s="14"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
       <c r="D560" s="2"/>
@@ -21896,7 +21887,7 @@
       <c r="Z560" s="3"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="15"/>
+      <c r="A561" s="14"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
       <c r="D561" s="2"/>
@@ -21924,7 +21915,7 @@
       <c r="Z561" s="3"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="15"/>
+      <c r="A562" s="14"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
       <c r="D562" s="2"/>
@@ -21952,7 +21943,7 @@
       <c r="Z562" s="3"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="15"/>
+      <c r="A563" s="14"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
       <c r="D563" s="2"/>
@@ -21980,7 +21971,7 @@
       <c r="Z563" s="3"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="15"/>
+      <c r="A564" s="14"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
       <c r="D564" s="2"/>
@@ -22008,7 +21999,7 @@
       <c r="Z564" s="3"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="15"/>
+      <c r="A565" s="14"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
       <c r="D565" s="2"/>
@@ -22036,7 +22027,7 @@
       <c r="Z565" s="3"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="15"/>
+      <c r="A566" s="14"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
       <c r="D566" s="2"/>
@@ -22064,7 +22055,7 @@
       <c r="Z566" s="3"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="15"/>
+      <c r="A567" s="14"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
       <c r="D567" s="2"/>
@@ -22092,7 +22083,7 @@
       <c r="Z567" s="3"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="15"/>
+      <c r="A568" s="14"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
       <c r="D568" s="2"/>
@@ -22120,7 +22111,7 @@
       <c r="Z568" s="3"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="15"/>
+      <c r="A569" s="14"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
       <c r="D569" s="2"/>
@@ -22148,7 +22139,7 @@
       <c r="Z569" s="3"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="15"/>
+      <c r="A570" s="14"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
       <c r="D570" s="2"/>
@@ -22176,7 +22167,7 @@
       <c r="Z570" s="3"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="15"/>
+      <c r="A571" s="14"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
       <c r="D571" s="2"/>
@@ -22204,7 +22195,7 @@
       <c r="Z571" s="3"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="15"/>
+      <c r="A572" s="14"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
       <c r="D572" s="2"/>
@@ -22232,7 +22223,7 @@
       <c r="Z572" s="3"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="15"/>
+      <c r="A573" s="14"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
       <c r="D573" s="2"/>
@@ -22260,7 +22251,7 @@
       <c r="Z573" s="3"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="15"/>
+      <c r="A574" s="14"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
       <c r="D574" s="2"/>
@@ -22288,7 +22279,7 @@
       <c r="Z574" s="3"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="15"/>
+      <c r="A575" s="14"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
       <c r="D575" s="2"/>
@@ -22316,7 +22307,7 @@
       <c r="Z575" s="3"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="15"/>
+      <c r="A576" s="14"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
       <c r="D576" s="2"/>
@@ -22344,7 +22335,7 @@
       <c r="Z576" s="3"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="15"/>
+      <c r="A577" s="14"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
       <c r="D577" s="2"/>
@@ -22372,7 +22363,7 @@
       <c r="Z577" s="3"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="15"/>
+      <c r="A578" s="14"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
       <c r="D578" s="2"/>
@@ -22400,7 +22391,7 @@
       <c r="Z578" s="3"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="15"/>
+      <c r="A579" s="14"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
       <c r="D579" s="2"/>
@@ -22428,7 +22419,7 @@
       <c r="Z579" s="3"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="15"/>
+      <c r="A580" s="14"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
       <c r="D580" s="2"/>
@@ -22456,7 +22447,7 @@
       <c r="Z580" s="3"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="15"/>
+      <c r="A581" s="14"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
       <c r="D581" s="2"/>
@@ -22484,7 +22475,7 @@
       <c r="Z581" s="3"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="15"/>
+      <c r="A582" s="14"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
       <c r="D582" s="2"/>
@@ -22512,7 +22503,7 @@
       <c r="Z582" s="3"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="15"/>
+      <c r="A583" s="14"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
       <c r="D583" s="2"/>
@@ -22540,7 +22531,7 @@
       <c r="Z583" s="3"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="15"/>
+      <c r="A584" s="14"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
       <c r="D584" s="2"/>
@@ -22568,7 +22559,7 @@
       <c r="Z584" s="3"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="15"/>
+      <c r="A585" s="14"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
       <c r="D585" s="2"/>
@@ -22596,7 +22587,7 @@
       <c r="Z585" s="3"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="15"/>
+      <c r="A586" s="14"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
       <c r="D586" s="2"/>
@@ -22624,7 +22615,7 @@
       <c r="Z586" s="3"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="15"/>
+      <c r="A587" s="14"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
       <c r="D587" s="2"/>
@@ -22652,7 +22643,7 @@
       <c r="Z587" s="3"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="15"/>
+      <c r="A588" s="14"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
       <c r="D588" s="2"/>
@@ -22680,7 +22671,7 @@
       <c r="Z588" s="3"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="15"/>
+      <c r="A589" s="14"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
       <c r="D589" s="2"/>
@@ -22708,7 +22699,7 @@
       <c r="Z589" s="3"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="15"/>
+      <c r="A590" s="14"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
       <c r="D590" s="2"/>
@@ -22736,7 +22727,7 @@
       <c r="Z590" s="3"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="15"/>
+      <c r="A591" s="14"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
       <c r="D591" s="2"/>
@@ -22764,7 +22755,7 @@
       <c r="Z591" s="3"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="15"/>
+      <c r="A592" s="14"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
       <c r="D592" s="2"/>
@@ -22792,7 +22783,7 @@
       <c r="Z592" s="3"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="15"/>
+      <c r="A593" s="14"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
       <c r="D593" s="2"/>
@@ -22820,7 +22811,7 @@
       <c r="Z593" s="3"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="15"/>
+      <c r="A594" s="14"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
       <c r="D594" s="2"/>
@@ -22848,7 +22839,7 @@
       <c r="Z594" s="3"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="15"/>
+      <c r="A595" s="14"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
       <c r="D595" s="2"/>
@@ -22876,7 +22867,7 @@
       <c r="Z595" s="3"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="15"/>
+      <c r="A596" s="14"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
       <c r="D596" s="2"/>
@@ -22904,7 +22895,7 @@
       <c r="Z596" s="3"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="15"/>
+      <c r="A597" s="14"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
       <c r="D597" s="2"/>
@@ -22932,7 +22923,7 @@
       <c r="Z597" s="3"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="15"/>
+      <c r="A598" s="14"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
       <c r="D598" s="2"/>
@@ -22960,7 +22951,7 @@
       <c r="Z598" s="3"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="15"/>
+      <c r="A599" s="14"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
       <c r="D599" s="2"/>
@@ -22988,7 +22979,7 @@
       <c r="Z599" s="3"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="15"/>
+      <c r="A600" s="14"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
       <c r="D600" s="2"/>
@@ -23016,7 +23007,7 @@
       <c r="Z600" s="3"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="15"/>
+      <c r="A601" s="14"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
       <c r="D601" s="2"/>
@@ -23044,7 +23035,7 @@
       <c r="Z601" s="3"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="15"/>
+      <c r="A602" s="14"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
       <c r="D602" s="2"/>
@@ -23072,7 +23063,7 @@
       <c r="Z602" s="3"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="15"/>
+      <c r="A603" s="14"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
       <c r="D603" s="2"/>
@@ -23100,7 +23091,7 @@
       <c r="Z603" s="3"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="15"/>
+      <c r="A604" s="14"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
       <c r="D604" s="2"/>
@@ -23128,7 +23119,7 @@
       <c r="Z604" s="3"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="15"/>
+      <c r="A605" s="14"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
       <c r="D605" s="2"/>
@@ -23156,7 +23147,7 @@
       <c r="Z605" s="3"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="15"/>
+      <c r="A606" s="14"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
       <c r="D606" s="2"/>
@@ -23184,7 +23175,7 @@
       <c r="Z606" s="3"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="15"/>
+      <c r="A607" s="14"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
       <c r="D607" s="2"/>
@@ -23212,7 +23203,7 @@
       <c r="Z607" s="3"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="15"/>
+      <c r="A608" s="14"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
       <c r="D608" s="2"/>
@@ -23240,7 +23231,7 @@
       <c r="Z608" s="3"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="15"/>
+      <c r="A609" s="14"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
       <c r="D609" s="2"/>
@@ -23268,7 +23259,7 @@
       <c r="Z609" s="3"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="15"/>
+      <c r="A610" s="14"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
       <c r="D610" s="2"/>
@@ -23296,7 +23287,7 @@
       <c r="Z610" s="3"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="15"/>
+      <c r="A611" s="14"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
       <c r="D611" s="2"/>
@@ -23324,7 +23315,7 @@
       <c r="Z611" s="3"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="15"/>
+      <c r="A612" s="14"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
       <c r="D612" s="2"/>
@@ -23352,7 +23343,7 @@
       <c r="Z612" s="3"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="15"/>
+      <c r="A613" s="14"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
       <c r="D613" s="2"/>
@@ -23380,7 +23371,7 @@
       <c r="Z613" s="3"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="15"/>
+      <c r="A614" s="14"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
       <c r="D614" s="2"/>
@@ -23408,7 +23399,7 @@
       <c r="Z614" s="3"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="15"/>
+      <c r="A615" s="14"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
       <c r="D615" s="2"/>
@@ -23436,7 +23427,7 @@
       <c r="Z615" s="3"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="15"/>
+      <c r="A616" s="14"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
       <c r="D616" s="2"/>
@@ -23464,7 +23455,7 @@
       <c r="Z616" s="3"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="15"/>
+      <c r="A617" s="14"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
       <c r="D617" s="2"/>
@@ -23492,7 +23483,7 @@
       <c r="Z617" s="3"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="15"/>
+      <c r="A618" s="14"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
       <c r="D618" s="2"/>
@@ -23520,7 +23511,7 @@
       <c r="Z618" s="3"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="15"/>
+      <c r="A619" s="14"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
       <c r="D619" s="2"/>
@@ -23548,7 +23539,7 @@
       <c r="Z619" s="3"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="15"/>
+      <c r="A620" s="14"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
       <c r="D620" s="2"/>
@@ -23576,7 +23567,7 @@
       <c r="Z620" s="3"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="15"/>
+      <c r="A621" s="14"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
       <c r="D621" s="2"/>
@@ -23604,7 +23595,7 @@
       <c r="Z621" s="3"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="15"/>
+      <c r="A622" s="14"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
       <c r="D622" s="2"/>
@@ -23632,7 +23623,7 @@
       <c r="Z622" s="3"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="15"/>
+      <c r="A623" s="14"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
       <c r="D623" s="2"/>
@@ -23660,7 +23651,7 @@
       <c r="Z623" s="3"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="15"/>
+      <c r="A624" s="14"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
       <c r="D624" s="2"/>
@@ -23688,7 +23679,7 @@
       <c r="Z624" s="3"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="15"/>
+      <c r="A625" s="14"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
       <c r="D625" s="2"/>
@@ -23716,7 +23707,7 @@
       <c r="Z625" s="3"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="15"/>
+      <c r="A626" s="14"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
       <c r="D626" s="2"/>
@@ -23744,7 +23735,7 @@
       <c r="Z626" s="3"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="15"/>
+      <c r="A627" s="14"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
       <c r="D627" s="2"/>
@@ -23772,7 +23763,7 @@
       <c r="Z627" s="3"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="15"/>
+      <c r="A628" s="14"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
       <c r="D628" s="2"/>
@@ -23800,7 +23791,7 @@
       <c r="Z628" s="3"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="15"/>
+      <c r="A629" s="14"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
       <c r="D629" s="2"/>
@@ -23828,7 +23819,7 @@
       <c r="Z629" s="3"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="15"/>
+      <c r="A630" s="14"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
       <c r="D630" s="2"/>
@@ -23856,7 +23847,7 @@
       <c r="Z630" s="3"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="15"/>
+      <c r="A631" s="14"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
       <c r="D631" s="2"/>
@@ -23884,7 +23875,7 @@
       <c r="Z631" s="3"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="15"/>
+      <c r="A632" s="14"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
       <c r="D632" s="2"/>
@@ -23912,7 +23903,7 @@
       <c r="Z632" s="3"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="15"/>
+      <c r="A633" s="14"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
       <c r="D633" s="2"/>
@@ -23940,7 +23931,7 @@
       <c r="Z633" s="3"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="15"/>
+      <c r="A634" s="14"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
       <c r="D634" s="2"/>
@@ -23968,7 +23959,7 @@
       <c r="Z634" s="3"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="15"/>
+      <c r="A635" s="14"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
       <c r="D635" s="2"/>
@@ -23996,7 +23987,7 @@
       <c r="Z635" s="3"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="15"/>
+      <c r="A636" s="14"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
       <c r="D636" s="2"/>
@@ -24024,7 +24015,7 @@
       <c r="Z636" s="3"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="15"/>
+      <c r="A637" s="14"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
       <c r="D637" s="2"/>
@@ -24052,7 +24043,7 @@
       <c r="Z637" s="3"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="15"/>
+      <c r="A638" s="14"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
       <c r="D638" s="2"/>
@@ -24080,7 +24071,7 @@
       <c r="Z638" s="3"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="15"/>
+      <c r="A639" s="14"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
       <c r="D639" s="2"/>
@@ -24108,7 +24099,7 @@
       <c r="Z639" s="3"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="15"/>
+      <c r="A640" s="14"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
       <c r="D640" s="2"/>
@@ -24136,7 +24127,7 @@
       <c r="Z640" s="3"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="15"/>
+      <c r="A641" s="14"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
       <c r="D641" s="2"/>
@@ -24164,7 +24155,7 @@
       <c r="Z641" s="3"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="15"/>
+      <c r="A642" s="14"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
       <c r="D642" s="2"/>
@@ -24192,7 +24183,7 @@
       <c r="Z642" s="3"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="15"/>
+      <c r="A643" s="14"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
       <c r="D643" s="2"/>
@@ -24220,7 +24211,7 @@
       <c r="Z643" s="3"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="15"/>
+      <c r="A644" s="14"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
       <c r="D644" s="2"/>
@@ -24248,7 +24239,7 @@
       <c r="Z644" s="3"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="15"/>
+      <c r="A645" s="14"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
       <c r="D645" s="2"/>
@@ -24276,7 +24267,7 @@
       <c r="Z645" s="3"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="15"/>
+      <c r="A646" s="14"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
       <c r="D646" s="2"/>
@@ -24304,7 +24295,7 @@
       <c r="Z646" s="3"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="15"/>
+      <c r="A647" s="14"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
       <c r="D647" s="2"/>
@@ -24332,7 +24323,7 @@
       <c r="Z647" s="3"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="15"/>
+      <c r="A648" s="14"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
       <c r="D648" s="2"/>
@@ -24360,7 +24351,7 @@
       <c r="Z648" s="3"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="15"/>
+      <c r="A649" s="14"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
       <c r="D649" s="2"/>
@@ -24388,7 +24379,7 @@
       <c r="Z649" s="3"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="15"/>
+      <c r="A650" s="14"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
       <c r="D650" s="2"/>
@@ -24416,7 +24407,7 @@
       <c r="Z650" s="3"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="15"/>
+      <c r="A651" s="14"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
       <c r="D651" s="2"/>
@@ -24444,7 +24435,7 @@
       <c r="Z651" s="3"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="15"/>
+      <c r="A652" s="14"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
       <c r="D652" s="2"/>
@@ -24472,7 +24463,7 @@
       <c r="Z652" s="3"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="15"/>
+      <c r="A653" s="14"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
       <c r="D653" s="2"/>
@@ -24500,7 +24491,7 @@
       <c r="Z653" s="3"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="15"/>
+      <c r="A654" s="14"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
       <c r="D654" s="2"/>
@@ -24528,7 +24519,7 @@
       <c r="Z654" s="3"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="15"/>
+      <c r="A655" s="14"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
       <c r="D655" s="2"/>
@@ -24556,7 +24547,7 @@
       <c r="Z655" s="3"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="15"/>
+      <c r="A656" s="14"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
       <c r="D656" s="2"/>
@@ -24584,7 +24575,7 @@
       <c r="Z656" s="3"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="15"/>
+      <c r="A657" s="14"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
       <c r="D657" s="2"/>
@@ -24612,7 +24603,7 @@
       <c r="Z657" s="3"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="15"/>
+      <c r="A658" s="14"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
       <c r="D658" s="2"/>
@@ -24640,7 +24631,7 @@
       <c r="Z658" s="3"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="15"/>
+      <c r="A659" s="14"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
       <c r="D659" s="2"/>
@@ -24668,7 +24659,7 @@
       <c r="Z659" s="3"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="15"/>
+      <c r="A660" s="14"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
       <c r="D660" s="2"/>
@@ -24696,7 +24687,7 @@
       <c r="Z660" s="3"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="15"/>
+      <c r="A661" s="14"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
       <c r="D661" s="2"/>
@@ -24724,7 +24715,7 @@
       <c r="Z661" s="3"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="15"/>
+      <c r="A662" s="14"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
       <c r="D662" s="2"/>
@@ -24752,7 +24743,7 @@
       <c r="Z662" s="3"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="15"/>
+      <c r="A663" s="14"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
       <c r="D663" s="2"/>
@@ -24780,7 +24771,7 @@
       <c r="Z663" s="3"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="15"/>
+      <c r="A664" s="14"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
       <c r="D664" s="2"/>
@@ -24808,7 +24799,7 @@
       <c r="Z664" s="3"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="15"/>
+      <c r="A665" s="14"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
       <c r="D665" s="2"/>
@@ -24836,7 +24827,7 @@
       <c r="Z665" s="3"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="15"/>
+      <c r="A666" s="14"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
       <c r="D666" s="2"/>
@@ -24864,7 +24855,7 @@
       <c r="Z666" s="3"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="15"/>
+      <c r="A667" s="14"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
       <c r="D667" s="2"/>
@@ -24892,7 +24883,7 @@
       <c r="Z667" s="3"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="15"/>
+      <c r="A668" s="14"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
       <c r="D668" s="2"/>
@@ -24920,7 +24911,7 @@
       <c r="Z668" s="3"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="15"/>
+      <c r="A669" s="14"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
       <c r="D669" s="2"/>
@@ -24948,7 +24939,7 @@
       <c r="Z669" s="3"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="15"/>
+      <c r="A670" s="14"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
       <c r="D670" s="2"/>
@@ -24976,7 +24967,7 @@
       <c r="Z670" s="3"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="15"/>
+      <c r="A671" s="14"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
       <c r="D671" s="2"/>
@@ -25004,7 +24995,7 @@
       <c r="Z671" s="3"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="15"/>
+      <c r="A672" s="14"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
       <c r="D672" s="2"/>
@@ -25032,7 +25023,7 @@
       <c r="Z672" s="3"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="15"/>
+      <c r="A673" s="14"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
       <c r="D673" s="2"/>
@@ -25060,7 +25051,7 @@
       <c r="Z673" s="3"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="15"/>
+      <c r="A674" s="14"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
       <c r="D674" s="2"/>
@@ -25088,7 +25079,7 @@
       <c r="Z674" s="3"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="15"/>
+      <c r="A675" s="14"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
       <c r="D675" s="2"/>
@@ -25116,7 +25107,7 @@
       <c r="Z675" s="3"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="15"/>
+      <c r="A676" s="14"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
       <c r="D676" s="2"/>
@@ -25144,7 +25135,7 @@
       <c r="Z676" s="3"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="15"/>
+      <c r="A677" s="14"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
       <c r="D677" s="2"/>
@@ -25172,7 +25163,7 @@
       <c r="Z677" s="3"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="15"/>
+      <c r="A678" s="14"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
       <c r="D678" s="2"/>
@@ -25200,7 +25191,7 @@
       <c r="Z678" s="3"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="15"/>
+      <c r="A679" s="14"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
       <c r="D679" s="2"/>
@@ -25228,7 +25219,7 @@
       <c r="Z679" s="3"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="15"/>
+      <c r="A680" s="14"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
       <c r="D680" s="2"/>
@@ -25256,7 +25247,7 @@
       <c r="Z680" s="3"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="15"/>
+      <c r="A681" s="14"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
       <c r="D681" s="2"/>
@@ -25284,7 +25275,7 @@
       <c r="Z681" s="3"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="15"/>
+      <c r="A682" s="14"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
       <c r="D682" s="2"/>
@@ -25312,7 +25303,7 @@
       <c r="Z682" s="3"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="15"/>
+      <c r="A683" s="14"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
       <c r="D683" s="2"/>
@@ -25340,7 +25331,7 @@
       <c r="Z683" s="3"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="15"/>
+      <c r="A684" s="14"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
       <c r="D684" s="2"/>
@@ -25368,7 +25359,7 @@
       <c r="Z684" s="3"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="15"/>
+      <c r="A685" s="14"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
       <c r="D685" s="2"/>
@@ -25396,7 +25387,7 @@
       <c r="Z685" s="3"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="15"/>
+      <c r="A686" s="14"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
       <c r="D686" s="2"/>
@@ -25424,7 +25415,7 @@
       <c r="Z686" s="3"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="15"/>
+      <c r="A687" s="14"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
       <c r="D687" s="2"/>
@@ -25452,7 +25443,7 @@
       <c r="Z687" s="3"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="15"/>
+      <c r="A688" s="14"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
       <c r="D688" s="2"/>
@@ -25480,7 +25471,7 @@
       <c r="Z688" s="3"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="15"/>
+      <c r="A689" s="14"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
       <c r="D689" s="2"/>
@@ -25508,7 +25499,7 @@
       <c r="Z689" s="3"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="15"/>
+      <c r="A690" s="14"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
       <c r="D690" s="2"/>
@@ -25536,7 +25527,7 @@
       <c r="Z690" s="3"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="15"/>
+      <c r="A691" s="14"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
       <c r="D691" s="2"/>
@@ -25564,7 +25555,7 @@
       <c r="Z691" s="3"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="15"/>
+      <c r="A692" s="14"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
       <c r="D692" s="2"/>
@@ -25592,7 +25583,7 @@
       <c r="Z692" s="3"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="15"/>
+      <c r="A693" s="14"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
       <c r="D693" s="2"/>
@@ -25620,7 +25611,7 @@
       <c r="Z693" s="3"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="15"/>
+      <c r="A694" s="14"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
       <c r="D694" s="2"/>
@@ -25648,7 +25639,7 @@
       <c r="Z694" s="3"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="15"/>
+      <c r="A695" s="14"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
       <c r="D695" s="2"/>
@@ -25676,7 +25667,7 @@
       <c r="Z695" s="3"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="15"/>
+      <c r="A696" s="14"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
       <c r="D696" s="2"/>
@@ -25704,7 +25695,7 @@
       <c r="Z696" s="3"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="15"/>
+      <c r="A697" s="14"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
       <c r="D697" s="2"/>
@@ -25732,7 +25723,7 @@
       <c r="Z697" s="3"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="15"/>
+      <c r="A698" s="14"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
       <c r="D698" s="2"/>
@@ -25760,7 +25751,7 @@
       <c r="Z698" s="3"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="15"/>
+      <c r="A699" s="14"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
       <c r="D699" s="2"/>
@@ -25788,7 +25779,7 @@
       <c r="Z699" s="3"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="15"/>
+      <c r="A700" s="14"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
       <c r="D700" s="2"/>
@@ -25816,7 +25807,7 @@
       <c r="Z700" s="3"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="15"/>
+      <c r="A701" s="14"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
       <c r="D701" s="2"/>
@@ -25844,7 +25835,7 @@
       <c r="Z701" s="3"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="15"/>
+      <c r="A702" s="14"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
       <c r="D702" s="2"/>
@@ -25872,7 +25863,7 @@
       <c r="Z702" s="3"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="15"/>
+      <c r="A703" s="14"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
       <c r="D703" s="2"/>
@@ -25900,7 +25891,7 @@
       <c r="Z703" s="3"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="15"/>
+      <c r="A704" s="14"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
       <c r="D704" s="2"/>
@@ -25928,7 +25919,7 @@
       <c r="Z704" s="3"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="15"/>
+      <c r="A705" s="14"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
       <c r="D705" s="2"/>
@@ -25956,7 +25947,7 @@
       <c r="Z705" s="3"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="15"/>
+      <c r="A706" s="14"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
       <c r="D706" s="2"/>
@@ -25984,7 +25975,7 @@
       <c r="Z706" s="3"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="15"/>
+      <c r="A707" s="14"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
       <c r="D707" s="2"/>
@@ -26012,7 +26003,7 @@
       <c r="Z707" s="3"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="15"/>
+      <c r="A708" s="14"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
       <c r="D708" s="2"/>
@@ -26040,7 +26031,7 @@
       <c r="Z708" s="3"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="15"/>
+      <c r="A709" s="14"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
       <c r="D709" s="2"/>
@@ -26068,7 +26059,7 @@
       <c r="Z709" s="3"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="15"/>
+      <c r="A710" s="14"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
       <c r="D710" s="2"/>
@@ -26096,7 +26087,7 @@
       <c r="Z710" s="3"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="15"/>
+      <c r="A711" s="14"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
       <c r="D711" s="2"/>
@@ -26124,7 +26115,7 @@
       <c r="Z711" s="3"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="15"/>
+      <c r="A712" s="14"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
       <c r="D712" s="2"/>
@@ -26152,7 +26143,7 @@
       <c r="Z712" s="3"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="15"/>
+      <c r="A713" s="14"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
       <c r="D713" s="2"/>
@@ -26180,7 +26171,7 @@
       <c r="Z713" s="3"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="15"/>
+      <c r="A714" s="14"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
       <c r="D714" s="2"/>
@@ -26208,7 +26199,7 @@
       <c r="Z714" s="3"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="15"/>
+      <c r="A715" s="14"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
       <c r="D715" s="2"/>
@@ -26236,7 +26227,7 @@
       <c r="Z715" s="3"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="15"/>
+      <c r="A716" s="14"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
       <c r="D716" s="2"/>
@@ -26264,7 +26255,7 @@
       <c r="Z716" s="3"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="15"/>
+      <c r="A717" s="14"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
       <c r="D717" s="2"/>
@@ -26292,7 +26283,7 @@
       <c r="Z717" s="3"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="15"/>
+      <c r="A718" s="14"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
       <c r="D718" s="2"/>
@@ -26320,7 +26311,7 @@
       <c r="Z718" s="3"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="15"/>
+      <c r="A719" s="14"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
       <c r="D719" s="2"/>
@@ -26348,7 +26339,7 @@
       <c r="Z719" s="3"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="15"/>
+      <c r="A720" s="14"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
       <c r="D720" s="2"/>
@@ -26376,7 +26367,7 @@
       <c r="Z720" s="3"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="15"/>
+      <c r="A721" s="14"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
       <c r="D721" s="2"/>
@@ -26404,7 +26395,7 @@
       <c r="Z721" s="3"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="15"/>
+      <c r="A722" s="14"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
       <c r="D722" s="2"/>
@@ -26432,7 +26423,7 @@
       <c r="Z722" s="3"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="15"/>
+      <c r="A723" s="14"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
       <c r="D723" s="2"/>
@@ -26460,7 +26451,7 @@
       <c r="Z723" s="3"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="15"/>
+      <c r="A724" s="14"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
       <c r="D724" s="2"/>
@@ -26488,7 +26479,7 @@
       <c r="Z724" s="3"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="15"/>
+      <c r="A725" s="14"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
       <c r="D725" s="2"/>
@@ -26516,7 +26507,7 @@
       <c r="Z725" s="3"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="15"/>
+      <c r="A726" s="14"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
       <c r="D726" s="2"/>
@@ -26544,7 +26535,7 @@
       <c r="Z726" s="3"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="15"/>
+      <c r="A727" s="14"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
       <c r="D727" s="2"/>
@@ -26572,7 +26563,7 @@
       <c r="Z727" s="3"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="15"/>
+      <c r="A728" s="14"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
       <c r="D728" s="2"/>
@@ -26600,7 +26591,7 @@
       <c r="Z728" s="3"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="15"/>
+      <c r="A729" s="14"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
       <c r="D729" s="2"/>
@@ -26628,7 +26619,7 @@
       <c r="Z729" s="3"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="15"/>
+      <c r="A730" s="14"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
       <c r="D730" s="2"/>
@@ -26656,7 +26647,7 @@
       <c r="Z730" s="3"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="15"/>
+      <c r="A731" s="14"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
       <c r="D731" s="2"/>
@@ -26684,7 +26675,7 @@
       <c r="Z731" s="3"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="15"/>
+      <c r="A732" s="14"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
       <c r="D732" s="2"/>
@@ -26712,7 +26703,7 @@
       <c r="Z732" s="3"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="15"/>
+      <c r="A733" s="14"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
       <c r="D733" s="2"/>
@@ -26740,7 +26731,7 @@
       <c r="Z733" s="3"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="15"/>
+      <c r="A734" s="14"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
       <c r="D734" s="2"/>
@@ -26768,7 +26759,7 @@
       <c r="Z734" s="3"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="15"/>
+      <c r="A735" s="14"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
       <c r="D735" s="2"/>
@@ -26796,7 +26787,7 @@
       <c r="Z735" s="3"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="15"/>
+      <c r="A736" s="14"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
       <c r="D736" s="2"/>
@@ -26824,7 +26815,7 @@
       <c r="Z736" s="3"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="15"/>
+      <c r="A737" s="14"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
       <c r="D737" s="2"/>
@@ -26852,7 +26843,7 @@
       <c r="Z737" s="3"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="15"/>
+      <c r="A738" s="14"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
       <c r="D738" s="2"/>
@@ -26880,7 +26871,7 @@
       <c r="Z738" s="3"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="15"/>
+      <c r="A739" s="14"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
       <c r="D739" s="2"/>
@@ -26908,7 +26899,7 @@
       <c r="Z739" s="3"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="15"/>
+      <c r="A740" s="14"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
       <c r="D740" s="2"/>
@@ -26936,7 +26927,7 @@
       <c r="Z740" s="3"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="15"/>
+      <c r="A741" s="14"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
       <c r="D741" s="2"/>
@@ -26964,7 +26955,7 @@
       <c r="Z741" s="3"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="15"/>
+      <c r="A742" s="14"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
       <c r="D742" s="2"/>
@@ -26992,7 +26983,7 @@
       <c r="Z742" s="3"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="15"/>
+      <c r="A743" s="14"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
       <c r="D743" s="2"/>
@@ -27020,7 +27011,7 @@
       <c r="Z743" s="3"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="15"/>
+      <c r="A744" s="14"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
       <c r="D744" s="2"/>
@@ -27048,7 +27039,7 @@
       <c r="Z744" s="3"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="15"/>
+      <c r="A745" s="14"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
       <c r="D745" s="2"/>
@@ -27076,7 +27067,7 @@
       <c r="Z745" s="3"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="15"/>
+      <c r="A746" s="14"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
       <c r="D746" s="2"/>
@@ -27104,7 +27095,7 @@
       <c r="Z746" s="3"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="15"/>
+      <c r="A747" s="14"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
       <c r="D747" s="2"/>
@@ -27132,7 +27123,7 @@
       <c r="Z747" s="3"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="15"/>
+      <c r="A748" s="14"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
       <c r="D748" s="2"/>
@@ -27160,7 +27151,7 @@
       <c r="Z748" s="3"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="15"/>
+      <c r="A749" s="14"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
       <c r="D749" s="2"/>
@@ -27188,7 +27179,7 @@
       <c r="Z749" s="3"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="15"/>
+      <c r="A750" s="14"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
       <c r="D750" s="2"/>
@@ -27216,7 +27207,7 @@
       <c r="Z750" s="3"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="15"/>
+      <c r="A751" s="14"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
       <c r="D751" s="2"/>
@@ -27244,7 +27235,7 @@
       <c r="Z751" s="3"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="15"/>
+      <c r="A752" s="14"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
       <c r="D752" s="2"/>
@@ -27272,7 +27263,7 @@
       <c r="Z752" s="3"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="15"/>
+      <c r="A753" s="14"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
       <c r="D753" s="2"/>
@@ -27300,7 +27291,7 @@
       <c r="Z753" s="3"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="15"/>
+      <c r="A754" s="14"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
       <c r="D754" s="2"/>
@@ -27328,7 +27319,7 @@
       <c r="Z754" s="3"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="15"/>
+      <c r="A755" s="14"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
       <c r="D755" s="2"/>
@@ -27356,7 +27347,7 @@
       <c r="Z755" s="3"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="15"/>
+      <c r="A756" s="14"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
       <c r="D756" s="2"/>
@@ -27384,7 +27375,7 @@
       <c r="Z756" s="3"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="15"/>
+      <c r="A757" s="14"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
       <c r="D757" s="2"/>
@@ -27412,7 +27403,7 @@
       <c r="Z757" s="3"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="15"/>
+      <c r="A758" s="14"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
       <c r="D758" s="2"/>
@@ -27440,7 +27431,7 @@
       <c r="Z758" s="3"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="15"/>
+      <c r="A759" s="14"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
       <c r="D759" s="2"/>
@@ -27468,7 +27459,7 @@
       <c r="Z759" s="3"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="15"/>
+      <c r="A760" s="14"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
       <c r="D760" s="2"/>
@@ -27496,7 +27487,7 @@
       <c r="Z760" s="3"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="15"/>
+      <c r="A761" s="14"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
       <c r="D761" s="2"/>
@@ -27524,7 +27515,7 @@
       <c r="Z761" s="3"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="15"/>
+      <c r="A762" s="14"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
       <c r="D762" s="2"/>
@@ -27552,7 +27543,7 @@
       <c r="Z762" s="3"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="15"/>
+      <c r="A763" s="14"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
       <c r="D763" s="2"/>
@@ -27580,7 +27571,7 @@
       <c r="Z763" s="3"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="15"/>
+      <c r="A764" s="14"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
       <c r="D764" s="2"/>
@@ -27608,7 +27599,7 @@
       <c r="Z764" s="3"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="15"/>
+      <c r="A765" s="14"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
       <c r="D765" s="2"/>
@@ -27636,7 +27627,7 @@
       <c r="Z765" s="3"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="15"/>
+      <c r="A766" s="14"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
       <c r="D766" s="2"/>
@@ -27664,7 +27655,7 @@
       <c r="Z766" s="3"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="15"/>
+      <c r="A767" s="14"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
       <c r="D767" s="2"/>
@@ -27692,7 +27683,7 @@
       <c r="Z767" s="3"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="15"/>
+      <c r="A768" s="14"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
       <c r="D768" s="2"/>
@@ -27720,7 +27711,7 @@
       <c r="Z768" s="3"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="15"/>
+      <c r="A769" s="14"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
       <c r="D769" s="2"/>
@@ -27748,7 +27739,7 @@
       <c r="Z769" s="3"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="15"/>
+      <c r="A770" s="14"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
       <c r="D770" s="2"/>
@@ -27776,7 +27767,7 @@
       <c r="Z770" s="3"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="15"/>
+      <c r="A771" s="14"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
       <c r="D771" s="2"/>
@@ -27804,7 +27795,7 @@
       <c r="Z771" s="3"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="15"/>
+      <c r="A772" s="14"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
       <c r="D772" s="2"/>
@@ -27832,7 +27823,7 @@
       <c r="Z772" s="3"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="15"/>
+      <c r="A773" s="14"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
       <c r="D773" s="2"/>
@@ -27860,7 +27851,7 @@
       <c r="Z773" s="3"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="15"/>
+      <c r="A774" s="14"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
       <c r="D774" s="2"/>
@@ -27888,7 +27879,7 @@
       <c r="Z774" s="3"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="15"/>
+      <c r="A775" s="14"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
       <c r="D775" s="2"/>
@@ -27916,7 +27907,7 @@
       <c r="Z775" s="3"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="15"/>
+      <c r="A776" s="14"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
       <c r="D776" s="2"/>
@@ -27944,7 +27935,7 @@
       <c r="Z776" s="3"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="15"/>
+      <c r="A777" s="14"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
       <c r="D777" s="2"/>
@@ -27972,7 +27963,7 @@
       <c r="Z777" s="3"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="15"/>
+      <c r="A778" s="14"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
       <c r="D778" s="2"/>
@@ -28000,7 +27991,7 @@
       <c r="Z778" s="3"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="15"/>
+      <c r="A779" s="14"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
       <c r="D779" s="2"/>
@@ -28028,7 +28019,7 @@
       <c r="Z779" s="3"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="15"/>
+      <c r="A780" s="14"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
       <c r="D780" s="2"/>
@@ -28056,7 +28047,7 @@
       <c r="Z780" s="3"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="15"/>
+      <c r="A781" s="14"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
       <c r="D781" s="2"/>
@@ -28084,7 +28075,7 @@
       <c r="Z781" s="3"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="15"/>
+      <c r="A782" s="14"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
       <c r="D782" s="2"/>
@@ -28112,7 +28103,7 @@
       <c r="Z782" s="3"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="15"/>
+      <c r="A783" s="14"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
       <c r="D783" s="2"/>
@@ -28140,7 +28131,7 @@
       <c r="Z783" s="3"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="15"/>
+      <c r="A784" s="14"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
       <c r="D784" s="2"/>
@@ -28168,7 +28159,7 @@
       <c r="Z784" s="3"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="15"/>
+      <c r="A785" s="14"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
       <c r="D785" s="2"/>
@@ -28196,7 +28187,7 @@
       <c r="Z785" s="3"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="15"/>
+      <c r="A786" s="14"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
       <c r="D786" s="2"/>
@@ -28224,7 +28215,7 @@
       <c r="Z786" s="3"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="15"/>
+      <c r="A787" s="14"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
       <c r="D787" s="2"/>
@@ -28252,7 +28243,7 @@
       <c r="Z787" s="3"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="15"/>
+      <c r="A788" s="14"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
       <c r="D788" s="2"/>
@@ -28280,7 +28271,7 @@
       <c r="Z788" s="3"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="15"/>
+      <c r="A789" s="14"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
       <c r="D789" s="2"/>
@@ -28308,7 +28299,7 @@
       <c r="Z789" s="3"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="15"/>
+      <c r="A790" s="14"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
       <c r="D790" s="2"/>
@@ -28336,7 +28327,7 @@
       <c r="Z790" s="3"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="15"/>
+      <c r="A791" s="14"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
       <c r="D791" s="2"/>
@@ -28364,7 +28355,7 @@
       <c r="Z791" s="3"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="15"/>
+      <c r="A792" s="14"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
       <c r="D792" s="2"/>
@@ -28392,7 +28383,7 @@
       <c r="Z792" s="3"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="15"/>
+      <c r="A793" s="14"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
       <c r="D793" s="2"/>
@@ -28420,7 +28411,7 @@
       <c r="Z793" s="3"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="15"/>
+      <c r="A794" s="14"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
       <c r="D794" s="2"/>
@@ -28448,7 +28439,7 @@
       <c r="Z794" s="3"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="15"/>
+      <c r="A795" s="14"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
       <c r="D795" s="2"/>
@@ -28476,7 +28467,7 @@
       <c r="Z795" s="3"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="15"/>
+      <c r="A796" s="14"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
       <c r="D796" s="2"/>
@@ -28504,7 +28495,7 @@
       <c r="Z796" s="3"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="15"/>
+      <c r="A797" s="14"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
       <c r="D797" s="2"/>
@@ -28532,7 +28523,7 @@
       <c r="Z797" s="3"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="15"/>
+      <c r="A798" s="14"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
       <c r="D798" s="2"/>
@@ -28560,7 +28551,7 @@
       <c r="Z798" s="3"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="15"/>
+      <c r="A799" s="14"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
       <c r="D799" s="2"/>
@@ -28588,7 +28579,7 @@
       <c r="Z799" s="3"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="15"/>
+      <c r="A800" s="14"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
       <c r="D800" s="2"/>
@@ -28616,7 +28607,7 @@
       <c r="Z800" s="3"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="15"/>
+      <c r="A801" s="14"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
       <c r="D801" s="2"/>
@@ -28644,7 +28635,7 @@
       <c r="Z801" s="3"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="15"/>
+      <c r="A802" s="14"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
       <c r="D802" s="2"/>
@@ -28672,7 +28663,7 @@
       <c r="Z802" s="3"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="15"/>
+      <c r="A803" s="14"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
       <c r="D803" s="2"/>
@@ -28700,7 +28691,7 @@
       <c r="Z803" s="3"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="15"/>
+      <c r="A804" s="14"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
       <c r="D804" s="2"/>
@@ -28728,7 +28719,7 @@
       <c r="Z804" s="3"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="15"/>
+      <c r="A805" s="14"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
       <c r="D805" s="2"/>
@@ -28756,7 +28747,7 @@
       <c r="Z805" s="3"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="15"/>
+      <c r="A806" s="14"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
       <c r="D806" s="2"/>
@@ -28784,7 +28775,7 @@
       <c r="Z806" s="3"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="15"/>
+      <c r="A807" s="14"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
       <c r="D807" s="2"/>
@@ -28812,7 +28803,7 @@
       <c r="Z807" s="3"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="15"/>
+      <c r="A808" s="14"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
       <c r="D808" s="2"/>
@@ -28840,7 +28831,7 @@
       <c r="Z808" s="3"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="15"/>
+      <c r="A809" s="14"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
       <c r="D809" s="2"/>
@@ -28868,7 +28859,7 @@
       <c r="Z809" s="3"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="15"/>
+      <c r="A810" s="14"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
       <c r="D810" s="2"/>
@@ -28896,7 +28887,7 @@
       <c r="Z810" s="3"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="15"/>
+      <c r="A811" s="14"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
       <c r="D811" s="2"/>
@@ -28924,7 +28915,7 @@
       <c r="Z811" s="3"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="15"/>
+      <c r="A812" s="14"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
       <c r="D812" s="2"/>
@@ -28952,7 +28943,7 @@
       <c r="Z812" s="3"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="15"/>
+      <c r="A813" s="14"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
       <c r="D813" s="2"/>
@@ -28980,7 +28971,7 @@
       <c r="Z813" s="3"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="15"/>
+      <c r="A814" s="14"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
       <c r="D814" s="2"/>
@@ -29008,7 +28999,7 @@
       <c r="Z814" s="3"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="15"/>
+      <c r="A815" s="14"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
       <c r="D815" s="2"/>
@@ -29036,7 +29027,7 @@
       <c r="Z815" s="3"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="15"/>
+      <c r="A816" s="14"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
       <c r="D816" s="2"/>
@@ -29064,7 +29055,7 @@
       <c r="Z816" s="3"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="15"/>
+      <c r="A817" s="14"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
       <c r="D817" s="2"/>
@@ -29092,7 +29083,7 @@
       <c r="Z817" s="3"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="15"/>
+      <c r="A818" s="14"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
       <c r="D818" s="2"/>
@@ -29120,7 +29111,7 @@
       <c r="Z818" s="3"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="15"/>
+      <c r="A819" s="14"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
       <c r="D819" s="2"/>
@@ -29148,7 +29139,7 @@
       <c r="Z819" s="3"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="15"/>
+      <c r="A820" s="14"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
       <c r="D820" s="2"/>
@@ -29176,7 +29167,7 @@
       <c r="Z820" s="3"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="15"/>
+      <c r="A821" s="14"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
       <c r="D821" s="2"/>
@@ -29204,7 +29195,7 @@
       <c r="Z821" s="3"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="15"/>
+      <c r="A822" s="14"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
       <c r="D822" s="2"/>
@@ -29232,7 +29223,7 @@
       <c r="Z822" s="3"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="15"/>
+      <c r="A823" s="14"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
       <c r="D823" s="2"/>
@@ -29260,7 +29251,7 @@
       <c r="Z823" s="3"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="15"/>
+      <c r="A824" s="14"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
       <c r="D824" s="2"/>
@@ -29288,7 +29279,7 @@
       <c r="Z824" s="3"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="15"/>
+      <c r="A825" s="14"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
       <c r="D825" s="2"/>
@@ -29316,7 +29307,7 @@
       <c r="Z825" s="3"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="15"/>
+      <c r="A826" s="14"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
       <c r="D826" s="2"/>
@@ -29344,7 +29335,7 @@
       <c r="Z826" s="3"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="15"/>
+      <c r="A827" s="14"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
       <c r="D827" s="2"/>
@@ -29372,7 +29363,7 @@
       <c r="Z827" s="3"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="15"/>
+      <c r="A828" s="14"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
       <c r="D828" s="2"/>
@@ -29400,7 +29391,7 @@
       <c r="Z828" s="3"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="15"/>
+      <c r="A829" s="14"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
       <c r="D829" s="2"/>
@@ -29428,7 +29419,7 @@
       <c r="Z829" s="3"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="15"/>
+      <c r="A830" s="14"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
       <c r="D830" s="2"/>
@@ -29456,7 +29447,7 @@
       <c r="Z830" s="3"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="15"/>
+      <c r="A831" s="14"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
       <c r="D831" s="2"/>
@@ -29484,7 +29475,7 @@
       <c r="Z831" s="3"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="15"/>
+      <c r="A832" s="14"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
       <c r="D832" s="2"/>
@@ -29512,7 +29503,7 @@
       <c r="Z832" s="3"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="15"/>
+      <c r="A833" s="14"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
       <c r="D833" s="2"/>
@@ -29540,7 +29531,7 @@
       <c r="Z833" s="3"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="15"/>
+      <c r="A834" s="14"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
       <c r="D834" s="2"/>
@@ -29568,7 +29559,7 @@
       <c r="Z834" s="3"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="15"/>
+      <c r="A835" s="14"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
       <c r="D835" s="2"/>
@@ -29596,7 +29587,7 @@
       <c r="Z835" s="3"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="15"/>
+      <c r="A836" s="14"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
       <c r="D836" s="2"/>
@@ -29624,7 +29615,7 @@
       <c r="Z836" s="3"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="15"/>
+      <c r="A837" s="14"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
       <c r="D837" s="2"/>
@@ -29652,7 +29643,7 @@
       <c r="Z837" s="3"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="15"/>
+      <c r="A838" s="14"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
       <c r="D838" s="2"/>
@@ -29680,7 +29671,7 @@
       <c r="Z838" s="3"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="15"/>
+      <c r="A839" s="14"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
       <c r="D839" s="2"/>
@@ -29708,7 +29699,7 @@
       <c r="Z839" s="3"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="15"/>
+      <c r="A840" s="14"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
       <c r="D840" s="2"/>
@@ -29736,7 +29727,7 @@
       <c r="Z840" s="3"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="15"/>
+      <c r="A841" s="14"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
       <c r="D841" s="2"/>
@@ -29764,7 +29755,7 @@
       <c r="Z841" s="3"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="15"/>
+      <c r="A842" s="14"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
       <c r="D842" s="2"/>
@@ -29792,7 +29783,7 @@
       <c r="Z842" s="3"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="15"/>
+      <c r="A843" s="14"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
       <c r="D843" s="2"/>
@@ -29820,7 +29811,7 @@
       <c r="Z843" s="3"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="15"/>
+      <c r="A844" s="14"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
       <c r="D844" s="2"/>
@@ -29848,7 +29839,7 @@
       <c r="Z844" s="3"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="15"/>
+      <c r="A845" s="14"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
       <c r="D845" s="2"/>
@@ -29876,7 +29867,7 @@
       <c r="Z845" s="3"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="15"/>
+      <c r="A846" s="14"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
       <c r="D846" s="2"/>
@@ -29904,7 +29895,7 @@
       <c r="Z846" s="3"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="15"/>
+      <c r="A847" s="14"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
       <c r="D847" s="2"/>
@@ -29932,7 +29923,7 @@
       <c r="Z847" s="3"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="15"/>
+      <c r="A848" s="14"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
       <c r="D848" s="2"/>
@@ -29960,7 +29951,7 @@
       <c r="Z848" s="3"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="15"/>
+      <c r="A849" s="14"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
       <c r="D849" s="2"/>
@@ -29988,7 +29979,7 @@
       <c r="Z849" s="3"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="15"/>
+      <c r="A850" s="14"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
       <c r="D850" s="2"/>
@@ -30016,7 +30007,7 @@
       <c r="Z850" s="3"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="15"/>
+      <c r="A851" s="14"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
       <c r="D851" s="2"/>
@@ -30044,7 +30035,7 @@
       <c r="Z851" s="3"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="15"/>
+      <c r="A852" s="14"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
       <c r="D852" s="2"/>
@@ -30072,7 +30063,7 @@
       <c r="Z852" s="3"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="15"/>
+      <c r="A853" s="14"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
       <c r="D853" s="2"/>
@@ -30100,7 +30091,7 @@
       <c r="Z853" s="3"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="15"/>
+      <c r="A854" s="14"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
       <c r="D854" s="2"/>
@@ -30128,7 +30119,7 @@
       <c r="Z854" s="3"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="15"/>
+      <c r="A855" s="14"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
       <c r="D855" s="2"/>
@@ -30156,7 +30147,7 @@
       <c r="Z855" s="3"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="15"/>
+      <c r="A856" s="14"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
       <c r="D856" s="2"/>
@@ -30184,7 +30175,7 @@
       <c r="Z856" s="3"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="15"/>
+      <c r="A857" s="14"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
       <c r="D857" s="2"/>
@@ -30212,7 +30203,7 @@
       <c r="Z857" s="3"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="15"/>
+      <c r="A858" s="14"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
       <c r="D858" s="2"/>
@@ -30240,7 +30231,7 @@
       <c r="Z858" s="3"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="15"/>
+      <c r="A859" s="14"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
       <c r="D859" s="2"/>
@@ -30268,7 +30259,7 @@
       <c r="Z859" s="3"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="15"/>
+      <c r="A860" s="14"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
       <c r="D860" s="2"/>
@@ -30296,7 +30287,7 @@
       <c r="Z860" s="3"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="15"/>
+      <c r="A861" s="14"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
       <c r="D861" s="2"/>
@@ -30324,7 +30315,7 @@
       <c r="Z861" s="3"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="15"/>
+      <c r="A862" s="14"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
       <c r="D862" s="2"/>
@@ -30352,7 +30343,7 @@
       <c r="Z862" s="3"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="15"/>
+      <c r="A863" s="14"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
       <c r="D863" s="2"/>
@@ -30380,7 +30371,7 @@
       <c r="Z863" s="3"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="15"/>
+      <c r="A864" s="14"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
       <c r="D864" s="2"/>
@@ -30408,7 +30399,7 @@
       <c r="Z864" s="3"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="15"/>
+      <c r="A865" s="14"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
       <c r="D865" s="2"/>
@@ -30436,7 +30427,7 @@
       <c r="Z865" s="3"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="15"/>
+      <c r="A866" s="14"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
       <c r="D866" s="2"/>
@@ -30464,7 +30455,7 @@
       <c r="Z866" s="3"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="15"/>
+      <c r="A867" s="14"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
       <c r="D867" s="2"/>
@@ -30492,7 +30483,7 @@
       <c r="Z867" s="3"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="15"/>
+      <c r="A868" s="14"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
       <c r="D868" s="2"/>
@@ -30520,7 +30511,7 @@
       <c r="Z868" s="3"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="15"/>
+      <c r="A869" s="14"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
       <c r="D869" s="2"/>
@@ -30548,7 +30539,7 @@
       <c r="Z869" s="3"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="15"/>
+      <c r="A870" s="14"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
       <c r="D870" s="2"/>
@@ -30576,7 +30567,7 @@
       <c r="Z870" s="3"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="15"/>
+      <c r="A871" s="14"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
       <c r="D871" s="2"/>
@@ -30604,7 +30595,7 @@
       <c r="Z871" s="3"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="15"/>
+      <c r="A872" s="14"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
       <c r="D872" s="2"/>
@@ -30632,7 +30623,7 @@
       <c r="Z872" s="3"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="15"/>
+      <c r="A873" s="14"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
       <c r="D873" s="2"/>
@@ -30660,7 +30651,7 @@
       <c r="Z873" s="3"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="15"/>
+      <c r="A874" s="14"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
       <c r="D874" s="2"/>
@@ -30688,7 +30679,7 @@
       <c r="Z874" s="3"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="15"/>
+      <c r="A875" s="14"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
       <c r="D875" s="2"/>
@@ -30716,7 +30707,7 @@
       <c r="Z875" s="3"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="15"/>
+      <c r="A876" s="14"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
       <c r="D876" s="2"/>
@@ -30744,7 +30735,7 @@
       <c r="Z876" s="3"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="15"/>
+      <c r="A877" s="14"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
       <c r="D877" s="2"/>
@@ -30772,7 +30763,7 @@
       <c r="Z877" s="3"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="15"/>
+      <c r="A878" s="14"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
       <c r="D878" s="2"/>
@@ -30800,7 +30791,7 @@
       <c r="Z878" s="3"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="15"/>
+      <c r="A879" s="14"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
       <c r="D879" s="2"/>
@@ -30828,7 +30819,7 @@
       <c r="Z879" s="3"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="15"/>
+      <c r="A880" s="14"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
       <c r="D880" s="2"/>
@@ -30856,7 +30847,7 @@
       <c r="Z880" s="3"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="15"/>
+      <c r="A881" s="14"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
       <c r="D881" s="2"/>
@@ -30884,7 +30875,7 @@
       <c r="Z881" s="3"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="15"/>
+      <c r="A882" s="14"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
       <c r="D882" s="2"/>
@@ -30912,7 +30903,7 @@
       <c r="Z882" s="3"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="15"/>
+      <c r="A883" s="14"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
       <c r="D883" s="2"/>
@@ -30940,7 +30931,7 @@
       <c r="Z883" s="3"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="15"/>
+      <c r="A884" s="14"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
       <c r="D884" s="2"/>
@@ -30968,7 +30959,7 @@
       <c r="Z884" s="3"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="15"/>
+      <c r="A885" s="14"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
       <c r="D885" s="2"/>
@@ -30996,7 +30987,7 @@
       <c r="Z885" s="3"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="15"/>
+      <c r="A886" s="14"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
       <c r="D886" s="2"/>
@@ -31024,7 +31015,7 @@
       <c r="Z886" s="3"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="15"/>
+      <c r="A887" s="14"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
       <c r="D887" s="2"/>
@@ -31052,7 +31043,7 @@
       <c r="Z887" s="3"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="15"/>
+      <c r="A888" s="14"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
       <c r="D888" s="2"/>
@@ -31080,7 +31071,7 @@
       <c r="Z888" s="3"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="15"/>
+      <c r="A889" s="14"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
       <c r="D889" s="2"/>
@@ -31108,7 +31099,7 @@
       <c r="Z889" s="3"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="15"/>
+      <c r="A890" s="14"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
       <c r="D890" s="2"/>
@@ -31136,7 +31127,7 @@
       <c r="Z890" s="3"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="15"/>
+      <c r="A891" s="14"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
       <c r="D891" s="2"/>
@@ -31164,7 +31155,7 @@
       <c r="Z891" s="3"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="15"/>
+      <c r="A892" s="14"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
       <c r="D892" s="2"/>
@@ -31192,7 +31183,7 @@
       <c r="Z892" s="3"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="15"/>
+      <c r="A893" s="14"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
       <c r="D893" s="2"/>
@@ -31220,7 +31211,7 @@
       <c r="Z893" s="3"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="15"/>
+      <c r="A894" s="14"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
       <c r="D894" s="2"/>
@@ -31248,7 +31239,7 @@
       <c r="Z894" s="3"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="15"/>
+      <c r="A895" s="14"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
       <c r="D895" s="2"/>
@@ -31276,7 +31267,7 @@
       <c r="Z895" s="3"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="15"/>
+      <c r="A896" s="14"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
       <c r="D896" s="2"/>
@@ -31304,7 +31295,7 @@
       <c r="Z896" s="3"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="15"/>
+      <c r="A897" s="14"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
       <c r="D897" s="2"/>
@@ -31332,7 +31323,7 @@
       <c r="Z897" s="3"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="15"/>
+      <c r="A898" s="14"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
       <c r="D898" s="2"/>
@@ -31360,7 +31351,7 @@
       <c r="Z898" s="3"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="15"/>
+      <c r="A899" s="14"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
       <c r="D899" s="2"/>
@@ -31388,7 +31379,7 @@
       <c r="Z899" s="3"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="15"/>
+      <c r="A900" s="14"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
       <c r="D900" s="2"/>
@@ -31416,7 +31407,7 @@
       <c r="Z900" s="3"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="15"/>
+      <c r="A901" s="14"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
       <c r="D901" s="2"/>
@@ -31444,7 +31435,7 @@
       <c r="Z901" s="3"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="15"/>
+      <c r="A902" s="14"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
       <c r="D902" s="2"/>
@@ -31472,7 +31463,7 @@
       <c r="Z902" s="3"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="15"/>
+      <c r="A903" s="14"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
       <c r="D903" s="2"/>
@@ -31500,7 +31491,7 @@
       <c r="Z903" s="3"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="15"/>
+      <c r="A904" s="14"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
       <c r="D904" s="2"/>
@@ -31528,7 +31519,7 @@
       <c r="Z904" s="3"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="15"/>
+      <c r="A905" s="14"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
       <c r="D905" s="2"/>
@@ -31556,7 +31547,7 @@
       <c r="Z905" s="3"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="15"/>
+      <c r="A906" s="14"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
       <c r="D906" s="2"/>
@@ -31584,7 +31575,7 @@
       <c r="Z906" s="3"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="15"/>
+      <c r="A907" s="14"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
       <c r="D907" s="2"/>
@@ -31612,7 +31603,7 @@
       <c r="Z907" s="3"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="15"/>
+      <c r="A908" s="14"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
       <c r="D908" s="2"/>
@@ -31640,7 +31631,7 @@
       <c r="Z908" s="3"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="15"/>
+      <c r="A909" s="14"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
       <c r="D909" s="2"/>
@@ -31668,7 +31659,7 @@
       <c r="Z909" s="3"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="15"/>
+      <c r="A910" s="14"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
       <c r="D910" s="2"/>
@@ -31696,7 +31687,7 @@
       <c r="Z910" s="3"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="15"/>
+      <c r="A911" s="14"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
       <c r="D911" s="2"/>
@@ -31724,7 +31715,7 @@
       <c r="Z911" s="3"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="15"/>
+      <c r="A912" s="14"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
       <c r="D912" s="2"/>
@@ -31752,7 +31743,7 @@
       <c r="Z912" s="3"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="15"/>
+      <c r="A913" s="14"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
       <c r="D913" s="2"/>
@@ -31780,7 +31771,7 @@
       <c r="Z913" s="3"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="15"/>
+      <c r="A914" s="14"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
       <c r="D914" s="2"/>
@@ -31808,7 +31799,7 @@
       <c r="Z914" s="3"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="15"/>
+      <c r="A915" s="14"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
       <c r="D915" s="2"/>
@@ -31836,7 +31827,7 @@
       <c r="Z915" s="3"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="15"/>
+      <c r="A916" s="14"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
       <c r="D916" s="2"/>
@@ -31864,7 +31855,7 @@
       <c r="Z916" s="3"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="15"/>
+      <c r="A917" s="14"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
       <c r="D917" s="2"/>
@@ -31892,7 +31883,7 @@
       <c r="Z917" s="3"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="15"/>
+      <c r="A918" s="14"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
       <c r="D918" s="2"/>
@@ -31920,7 +31911,7 @@
       <c r="Z918" s="3"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="15"/>
+      <c r="A919" s="14"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
       <c r="D919" s="2"/>
@@ -31948,7 +31939,7 @@
       <c r="Z919" s="3"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="15"/>
+      <c r="A920" s="14"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
       <c r="D920" s="2"/>
@@ -31976,7 +31967,7 @@
       <c r="Z920" s="3"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="15"/>
+      <c r="A921" s="14"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
       <c r="D921" s="2"/>
@@ -32004,7 +31995,7 @@
       <c r="Z921" s="3"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="15"/>
+      <c r="A922" s="14"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
       <c r="D922" s="2"/>
@@ -32032,7 +32023,7 @@
       <c r="Z922" s="3"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="15"/>
+      <c r="A923" s="14"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
       <c r="D923" s="2"/>
@@ -32060,7 +32051,7 @@
       <c r="Z923" s="3"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="15"/>
+      <c r="A924" s="14"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
       <c r="D924" s="2"/>
@@ -32088,7 +32079,7 @@
       <c r="Z924" s="3"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="15"/>
+      <c r="A925" s="14"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
       <c r="D925" s="2"/>
@@ -32116,7 +32107,7 @@
       <c r="Z925" s="3"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="15"/>
+      <c r="A926" s="14"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
       <c r="D926" s="2"/>
@@ -32144,7 +32135,7 @@
       <c r="Z926" s="3"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="15"/>
+      <c r="A927" s="14"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
       <c r="D927" s="2"/>
@@ -32172,7 +32163,7 @@
       <c r="Z927" s="3"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="15"/>
+      <c r="A928" s="14"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
       <c r="D928" s="2"/>
@@ -32200,7 +32191,7 @@
       <c r="Z928" s="3"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="15"/>
+      <c r="A929" s="14"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
       <c r="D929" s="2"/>
@@ -32228,7 +32219,7 @@
       <c r="Z929" s="3"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="15"/>
+      <c r="A930" s="14"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
       <c r="D930" s="2"/>
@@ -32256,7 +32247,7 @@
       <c r="Z930" s="3"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="15"/>
+      <c r="A931" s="14"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
       <c r="D931" s="2"/>
@@ -32284,7 +32275,7 @@
       <c r="Z931" s="3"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="15"/>
+      <c r="A932" s="14"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
       <c r="D932" s="2"/>
@@ -32312,7 +32303,7 @@
       <c r="Z932" s="3"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="15"/>
+      <c r="A933" s="14"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
       <c r="D933" s="2"/>
@@ -32340,7 +32331,7 @@
       <c r="Z933" s="3"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="15"/>
+      <c r="A934" s="14"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
       <c r="D934" s="2"/>
@@ -32368,7 +32359,7 @@
       <c r="Z934" s="3"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="15"/>
+      <c r="A935" s="14"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
       <c r="D935" s="2"/>
@@ -32396,7 +32387,7 @@
       <c r="Z935" s="3"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="15"/>
+      <c r="A936" s="14"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
       <c r="D936" s="2"/>
@@ -32424,7 +32415,7 @@
       <c r="Z936" s="3"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="15"/>
+      <c r="A937" s="14"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
       <c r="D937" s="2"/>
@@ -32452,7 +32443,7 @@
       <c r="Z937" s="3"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="15"/>
+      <c r="A938" s="14"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
       <c r="D938" s="2"/>
@@ -32480,7 +32471,7 @@
       <c r="Z938" s="3"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="15"/>
+      <c r="A939" s="14"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
       <c r="D939" s="2"/>
@@ -32508,7 +32499,7 @@
       <c r="Z939" s="3"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="15"/>
+      <c r="A940" s="14"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
       <c r="D940" s="2"/>
@@ -32536,7 +32527,7 @@
       <c r="Z940" s="3"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="15"/>
+      <c r="A941" s="14"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
       <c r="D941" s="2"/>
@@ -32564,7 +32555,7 @@
       <c r="Z941" s="3"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="15"/>
+      <c r="A942" s="14"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
       <c r="D942" s="2"/>
@@ -32592,7 +32583,7 @@
       <c r="Z942" s="3"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="15"/>
+      <c r="A943" s="14"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
       <c r="D943" s="2"/>
@@ -32620,7 +32611,7 @@
       <c r="Z943" s="3"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="15"/>
+      <c r="A944" s="14"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
       <c r="D944" s="2"/>
@@ -32648,7 +32639,7 @@
       <c r="Z944" s="3"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="15"/>
+      <c r="A945" s="14"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
       <c r="D945" s="2"/>
@@ -32676,7 +32667,7 @@
       <c r="Z945" s="3"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="15"/>
+      <c r="A946" s="14"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
       <c r="D946" s="2"/>
@@ -32704,7 +32695,7 @@
       <c r="Z946" s="3"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="15"/>
+      <c r="A947" s="14"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
       <c r="D947" s="2"/>
@@ -32732,7 +32723,7 @@
       <c r="Z947" s="3"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="15"/>
+      <c r="A948" s="14"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
       <c r="D948" s="2"/>
@@ -32760,7 +32751,7 @@
       <c r="Z948" s="3"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="15"/>
+      <c r="A949" s="14"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
       <c r="D949" s="2"/>
@@ -32788,7 +32779,7 @@
       <c r="Z949" s="3"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="15"/>
+      <c r="A950" s="14"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
       <c r="D950" s="2"/>
@@ -32816,7 +32807,7 @@
       <c r="Z950" s="3"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="15"/>
+      <c r="A951" s="14"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
       <c r="D951" s="2"/>
@@ -32844,7 +32835,7 @@
       <c r="Z951" s="3"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="15"/>
+      <c r="A952" s="14"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
       <c r="D952" s="2"/>
@@ -32872,7 +32863,7 @@
       <c r="Z952" s="3"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="15"/>
+      <c r="A953" s="14"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
       <c r="D953" s="2"/>
@@ -32900,7 +32891,7 @@
       <c r="Z953" s="3"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="15"/>
+      <c r="A954" s="14"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
       <c r="D954" s="2"/>
@@ -32928,7 +32919,7 @@
       <c r="Z954" s="3"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="15"/>
+      <c r="A955" s="14"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
       <c r="D955" s="2"/>
@@ -32956,7 +32947,7 @@
       <c r="Z955" s="3"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="15"/>
+      <c r="A956" s="14"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
       <c r="D956" s="2"/>
@@ -32984,7 +32975,7 @@
       <c r="Z956" s="3"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="15"/>
+      <c r="A957" s="14"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
       <c r="D957" s="2"/>
@@ -33012,7 +33003,7 @@
       <c r="Z957" s="3"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="15"/>
+      <c r="A958" s="14"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
       <c r="D958" s="2"/>
@@ -33040,7 +33031,7 @@
       <c r="Z958" s="3"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="15"/>
+      <c r="A959" s="14"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
       <c r="D959" s="2"/>
@@ -33068,7 +33059,7 @@
       <c r="Z959" s="3"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="15"/>
+      <c r="A960" s="14"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
       <c r="D960" s="2"/>
@@ -33096,7 +33087,7 @@
       <c r="Z960" s="3"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="15"/>
+      <c r="A961" s="14"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
       <c r="D961" s="2"/>
@@ -33124,7 +33115,7 @@
       <c r="Z961" s="3"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="15"/>
+      <c r="A962" s="14"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
       <c r="D962" s="2"/>
@@ -33152,7 +33143,7 @@
       <c r="Z962" s="3"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="15"/>
+      <c r="A963" s="14"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
       <c r="D963" s="2"/>
@@ -33180,7 +33171,7 @@
       <c r="Z963" s="3"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="15"/>
+      <c r="A964" s="14"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
       <c r="D964" s="2"/>
@@ -33208,7 +33199,7 @@
       <c r="Z964" s="3"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="15"/>
+      <c r="A965" s="14"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
       <c r="D965" s="2"/>
@@ -33236,7 +33227,7 @@
       <c r="Z965" s="3"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="15"/>
+      <c r="A966" s="14"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
       <c r="D966" s="2"/>
@@ -33264,7 +33255,7 @@
       <c r="Z966" s="3"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="15"/>
+      <c r="A967" s="14"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
       <c r="D967" s="2"/>
@@ -33292,7 +33283,7 @@
       <c r="Z967" s="3"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="15"/>
+      <c r="A968" s="14"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
       <c r="D968" s="2"/>
@@ -33320,7 +33311,7 @@
       <c r="Z968" s="3"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="15"/>
+      <c r="A969" s="14"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
       <c r="D969" s="2"/>
@@ -33348,7 +33339,7 @@
       <c r="Z969" s="3"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="15"/>
+      <c r="A970" s="14"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
       <c r="D970" s="2"/>
@@ -33376,7 +33367,7 @@
       <c r="Z970" s="3"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="15"/>
+      <c r="A971" s="14"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
       <c r="D971" s="2"/>
@@ -33404,7 +33395,7 @@
       <c r="Z971" s="3"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="15"/>
+      <c r="A972" s="14"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
       <c r="D972" s="2"/>
@@ -33432,7 +33423,7 @@
       <c r="Z972" s="3"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="15"/>
+      <c r="A973" s="14"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
       <c r="D973" s="2"/>
@@ -33460,7 +33451,7 @@
       <c r="Z973" s="3"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="15"/>
+      <c r="A974" s="14"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
       <c r="D974" s="2"/>
@@ -33488,7 +33479,7 @@
       <c r="Z974" s="3"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="15"/>
+      <c r="A975" s="14"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
       <c r="D975" s="2"/>
@@ -33516,7 +33507,7 @@
       <c r="Z975" s="3"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="15"/>
+      <c r="A976" s="14"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
       <c r="D976" s="2"/>
@@ -33544,7 +33535,7 @@
       <c r="Z976" s="3"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="15"/>
+      <c r="A977" s="14"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
       <c r="D977" s="2"/>
@@ -33572,7 +33563,7 @@
       <c r="Z977" s="3"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="15"/>
+      <c r="A978" s="14"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
       <c r="D978" s="2"/>
@@ -33600,7 +33591,7 @@
       <c r="Z978" s="3"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="15"/>
+      <c r="A979" s="14"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
       <c r="D979" s="2"/>
@@ -33628,7 +33619,7 @@
       <c r="Z979" s="3"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="15"/>
+      <c r="A980" s="14"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
       <c r="D980" s="2"/>
@@ -33656,7 +33647,7 @@
       <c r="Z980" s="3"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="15"/>
+      <c r="A981" s="14"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
       <c r="D981" s="2"/>
@@ -33684,7 +33675,7 @@
       <c r="Z981" s="3"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="15"/>
+      <c r="A982" s="14"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
       <c r="D982" s="2"/>
@@ -33712,7 +33703,7 @@
       <c r="Z982" s="3"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="15"/>
+      <c r="A983" s="14"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
       <c r="D983" s="2"/>
@@ -33740,7 +33731,7 @@
       <c r="Z983" s="3"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="15"/>
+      <c r="A984" s="14"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
       <c r="D984" s="2"/>
@@ -33768,7 +33759,7 @@
       <c r="Z984" s="3"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="15"/>
+      <c r="A985" s="14"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
       <c r="D985" s="2"/>
@@ -33796,7 +33787,7 @@
       <c r="Z985" s="3"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="15"/>
+      <c r="A986" s="14"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
       <c r="D986" s="2"/>
@@ -33824,7 +33815,7 @@
       <c r="Z986" s="3"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="15"/>
+      <c r="A987" s="14"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
       <c r="D987" s="2"/>
@@ -33852,7 +33843,7 @@
       <c r="Z987" s="3"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="15"/>
+      <c r="A988" s="14"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
       <c r="D988" s="2"/>
@@ -33880,7 +33871,7 @@
       <c r="Z988" s="3"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="15"/>
+      <c r="A989" s="14"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
       <c r="D989" s="2"/>
@@ -33908,7 +33899,7 @@
       <c r="Z989" s="3"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="15"/>
+      <c r="A990" s="14"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
       <c r="D990" s="2"/>
@@ -33936,7 +33927,7 @@
       <c r="Z990" s="3"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="15"/>
+      <c r="A991" s="14"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
       <c r="D991" s="2"/>
@@ -33964,7 +33955,7 @@
       <c r="Z991" s="3"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="15"/>
+      <c r="A992" s="14"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
       <c r="D992" s="2"/>
@@ -33992,7 +33983,7 @@
       <c r="Z992" s="3"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="15"/>
+      <c r="A993" s="14"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
       <c r="D993" s="2"/>
@@ -34020,7 +34011,7 @@
       <c r="Z993" s="3"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="15"/>
+      <c r="A994" s="14"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
       <c r="D994" s="2"/>
@@ -34048,7 +34039,7 @@
       <c r="Z994" s="3"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="15"/>
+      <c r="A995" s="14"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
       <c r="D995" s="2"/>
@@ -34076,7 +34067,7 @@
       <c r="Z995" s="3"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="15"/>
+      <c r="A996" s="14"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
       <c r="D996" s="2"/>
@@ -34104,7 +34095,7 @@
       <c r="Z996" s="3"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="15"/>
+      <c r="A997" s="14"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
       <c r="D997" s="2"/>
@@ -34132,7 +34123,7 @@
       <c r="Z997" s="3"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="15"/>
+      <c r="A998" s="14"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
       <c r="D998" s="2"/>
@@ -34160,7 +34151,7 @@
       <c r="Z998" s="3"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="15"/>
+      <c r="A999" s="14"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
       <c r="D999" s="2"/>
@@ -34188,7 +34179,7 @@
       <c r="Z999" s="3"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="15"/>
+      <c r="A1000" s="14"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
       <c r="D1000" s="2"/>
